--- a/Floor_Map_Simple.xlsx
+++ b/Floor_Map_Simple.xlsx
@@ -474,20 +474,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblStock" displayName="tblStock" ref="A4:H6" headerRowCount="1">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblStock" displayName="tblStock" ref="A4:F6" headerRowCount="1">
+  <tableColumns count="6">
     <tableColumn id="1" name="Item code"/>
     <tableColumn id="2" name="Description"/>
     <tableColumn id="3" name="Zone"/>
-    <tableColumn id="4" name="Units per pallet"/>
-    <tableColumn id="5" name="Low when pallets at or below"/>
-    <tableColumn id="6" name="Pallets on map">
+    <tableColumn id="4" name="Low when pallets at or below"/>
+    <tableColumn id="5" name="Pallets on map">
       <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$28,tblStock[[#This Row],[Item code]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="Units on map">
-      <calculatedColumnFormula>IF(OR(tblStock[[#This Row],[Item code]]="",N(tblStock[[#This Row],[Units per pallet]])=0),"",tblStock[[#This Row],[Pallets on map]]*tblStock[[#This Row],[Units per pallet]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" name="Status">
+    <tableColumn id="6" name="Status">
       <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -893,7 +889,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Click a square  ▶  click the little arrow  ▶  pick the item.      To empty a square: click it and press Delete.</t>
+          <t>Click a square  →  click the little arrow  →  pick the item.      To empty a square: click it and press Delete.</t>
         </is>
       </c>
     </row>
@@ -1921,21 +1917,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1949,13 +1943,11 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Type your items in the white columns. Grey columns fill in by themselves. Add a new item on the first empty row.</t>
+          <t>Everything is counted in PALLETS. Type your items in the white columns; grey columns fill in by themselves. Add a new item on the first empty row.</t>
         </is>
       </c>
     </row>
@@ -1977,45 +1969,35 @@
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>Units per pallet</t>
-        </is>
-      </c>
-      <c r="E4" s="27" t="inlineStr">
-        <is>
           <t>Low when pallets at or below</t>
         </is>
       </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Pallets on map</t>
+        </is>
+      </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>Pallets on map</t>
-        </is>
-      </c>
-      <c r="G4" s="28" t="inlineStr">
-        <is>
-          <t>Units on map</t>
-        </is>
-      </c>
-      <c r="H4" s="28" t="inlineStr">
-        <is>
           <t>Status</t>
         </is>
       </c>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>Spaces</t>
+        </is>
+      </c>
       <c r="J4" s="29" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Used</t>
         </is>
       </c>
       <c r="K4" s="29" t="inlineStr">
-        <is>
-          <t>Spaces</t>
-        </is>
-      </c>
-      <c r="L4" s="29" t="inlineStr">
-        <is>
-          <t>Used</t>
-        </is>
-      </c>
-      <c r="M4" s="29" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
@@ -2037,36 +2019,29 @@
           <t>BOX</t>
         </is>
       </c>
-      <c r="D5" s="32" t="n">
-        <v>400</v>
-      </c>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32">
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32">
         <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$28,tblStock[[#This Row],[Item code]]))</f>
         <v/>
       </c>
-      <c r="G5" s="32">
-        <f>IF(OR(tblStock[[#This Row],[Item code]]="",N(tblStock[[#This Row],[Units per pallet]])=0),"",tblStock[[#This Row],[Pallets on map]]*tblStock[[#This Row],[Units per pallet]])</f>
-        <v/>
-      </c>
-      <c r="H5" s="30">
+      <c r="F5" s="30">
         <f>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
         <v/>
       </c>
-      <c r="J5" s="33" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>Boxes</t>
         </is>
       </c>
-      <c r="K5" s="34" t="n">
+      <c r="I5" s="34" t="n">
         <v>256</v>
       </c>
-      <c r="L5" s="34">
+      <c r="J5" s="34">
         <f>COUNTA(Map!B18:Q21)+COUNTA(Map!B13:Q16)+COUNTA(Map!B8:Q11)+COUNTA(Map!U7:AJ10)</f>
         <v/>
       </c>
-      <c r="M5" s="35">
-        <f>K5-L5</f>
+      <c r="K5" s="35">
+        <f>I5-J5</f>
         <v/>
       </c>
     </row>
@@ -2086,86 +2061,79 @@
           <t>FLM</t>
         </is>
       </c>
-      <c r="D6" s="32" t="n">
-        <v>200</v>
-      </c>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="32">
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32">
         <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$28,tblStock[[#This Row],[Item code]]))</f>
         <v/>
       </c>
-      <c r="G6" s="32">
-        <f>IF(OR(tblStock[[#This Row],[Item code]]="",N(tblStock[[#This Row],[Units per pallet]])=0),"",tblStock[[#This Row],[Pallets on map]]*tblStock[[#This Row],[Units per pallet]])</f>
-        <v/>
-      </c>
-      <c r="H6" s="30">
+      <c r="F6" s="30">
         <f>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
         <v/>
       </c>
-      <c r="J6" s="36" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>Bags</t>
         </is>
       </c>
-      <c r="K6" s="34" t="n">
+      <c r="I6" s="34" t="n">
         <v>64</v>
       </c>
-      <c r="L6" s="34">
+      <c r="J6" s="34">
         <f>COUNTA(Map!U12:AJ15)</f>
         <v/>
       </c>
-      <c r="M6" s="35">
-        <f>K6-L6</f>
+      <c r="K6" s="35">
+        <f>I6-J6</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="J7" s="37" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>Films and Wrap</t>
         </is>
       </c>
-      <c r="K7" s="34" t="n">
+      <c r="I7" s="34" t="n">
         <v>64</v>
       </c>
-      <c r="L7" s="34">
+      <c r="J7" s="34">
         <f>COUNTA(Map!U17:AJ20)</f>
         <v/>
       </c>
-      <c r="M7" s="35">
-        <f>K7-L7</f>
+      <c r="K7" s="35">
+        <f>I7-J7</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="J8" s="38" t="inlineStr">
+      <c r="H8" s="38" t="inlineStr">
         <is>
           <t>Labels and Packing</t>
         </is>
       </c>
-      <c r="K8" s="34" t="n">
+      <c r="I8" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="L8" s="34">
+      <c r="J8" s="34">
         <f>COUNTA(Map!U22:AJ23)</f>
         <v/>
       </c>
-      <c r="M8" s="35">
-        <f>K8-L8</f>
+      <c r="K8" s="35">
+        <f>I8-J8</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H304">
+  <conditionalFormatting sqref="F5:F304">
     <cfRule type="expression" priority="1" dxfId="5">
-      <formula>H5="LOW"</formula>
+      <formula>F5="LOW"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="6">
-      <formula>H5="OK"</formula>
+      <formula>F5="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/Floor_Map_Simple.xlsx
+++ b/Floor_Map_Simple.xlsx
@@ -12,6 +12,10 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="zn_BOX">Stock!$I$5</definedName>
+    <definedName name="zn_BAG">Stock!$I$6</definedName>
+    <definedName name="zn_FLM">Stock!$I$7</definedName>
+    <definedName name="zn_LBL">Stock!$I$8</definedName>
     <definedName name="dd_ALL">OFFSET(Lists!$A$3,0,0,MAX(1,Lists!$A$2),1)</definedName>
     <definedName name="dd_BOX">OFFSET(Lists!$B$3,0,0,MAX(1,Lists!$B$2),1)</definedName>
     <definedName name="dd_BAG">OFFSET(Lists!$C$3,0,0,MAX(1,Lists!$C$2),1)</definedName>
@@ -28,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,13 +75,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E6007E"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00E6007E"/>
       <sz val="12"/>
     </font>
     <font>
@@ -133,6 +142,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C8A165"/>
+        <bgColor rgb="00C8A165"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A90D9"/>
+        <bgColor rgb="004A90D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002BB3A3"/>
+        <bgColor rgb="002BB3A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2B134"/>
+        <bgColor rgb="00F2B134"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0000843D"/>
         <bgColor rgb="0000843D"/>
       </patternFill>
@@ -169,36 +202,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8A165"/>
-        <bgColor rgb="00C8A165"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004A90D9"/>
-        <bgColor rgb="004A90D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002BB3A3"/>
-        <bgColor rgb="002BB3A3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2B134"/>
-        <bgColor rgb="00F2B134"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FF0000"/>
         <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -208,6 +217,20 @@
     </border>
     <border>
       <bottom style="thick">
+        <color rgb="00E6007E"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00E6007E"/>
+      </left>
+      <right style="medium">
+        <color rgb="00E6007E"/>
+      </right>
+      <top style="medium">
+        <color rgb="00E6007E"/>
+      </top>
+      <bottom style="medium">
         <color rgb="00E6007E"/>
       </bottom>
     </border>
@@ -229,63 +252,63 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -294,9 +317,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -307,16 +327,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -942,10 +968,9 @@
           <t>WALKWAY</t>
         </is>
       </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>R4   Boxes</t>
-        </is>
+      <c r="U6" s="7">
+        <f>"R4   "&amp;zn_BOX</f>
+        <v/>
       </c>
       <c r="AL6" s="8" t="inlineStr">
         <is>
@@ -963,10 +988,9 @@
       <c r="AU6" s="5" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>L3   Boxes</t>
-        </is>
+      <c r="B7" s="7">
+        <f>"L3   "&amp;zn_BOX</f>
+        <v/>
       </c>
       <c r="U7" s="9" t="n"/>
       <c r="V7" s="9" t="n"/>
@@ -985,10 +1009,9 @@
       <c r="AI7" s="9" t="n"/>
       <c r="AJ7" s="9" t="n"/>
       <c r="AL7" s="10" t="n"/>
-      <c r="AN7" s="11" t="inlineStr">
-        <is>
-          <t>Boxes</t>
-        </is>
+      <c r="AN7" s="11">
+        <f>zn_BOX</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -1025,10 +1048,9 @@
       <c r="AI8" s="9" t="n"/>
       <c r="AJ8" s="9" t="n"/>
       <c r="AL8" s="12" t="n"/>
-      <c r="AN8" s="11" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
+      <c r="AN8" s="11">
+        <f>zn_BAG</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -1065,10 +1087,9 @@
       <c r="AI9" s="9" t="n"/>
       <c r="AJ9" s="9" t="n"/>
       <c r="AL9" s="13" t="n"/>
-      <c r="AN9" s="11" t="inlineStr">
-        <is>
-          <t>Films and Wrap</t>
-        </is>
+      <c r="AN9" s="11">
+        <f>zn_FLM</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1105,10 +1126,9 @@
       <c r="AI10" s="9" t="n"/>
       <c r="AJ10" s="9" t="n"/>
       <c r="AL10" s="14" t="n"/>
-      <c r="AN10" s="11" t="inlineStr">
-        <is>
-          <t>Labels and Packing</t>
-        </is>
+      <c r="AN10" s="11">
+        <f>zn_LBL</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1128,10 +1148,9 @@
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>R3   Bags</t>
-        </is>
+      <c r="U11" s="7">
+        <f>"R3   "&amp;zn_BAG</f>
+        <v/>
       </c>
       <c r="AL11" s="15" t="n"/>
       <c r="AN11" s="11" t="inlineStr">
@@ -1141,10 +1160,9 @@
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>L2   Boxes</t>
-        </is>
+      <c r="B12" s="7">
+        <f>"L2   "&amp;zn_BOX</f>
+        <v/>
       </c>
       <c r="U12" s="16" t="n"/>
       <c r="V12" s="16" t="n"/>
@@ -1308,26 +1326,23 @@
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
       <c r="Q16" s="9" t="n"/>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>R2   Films and Wrap</t>
-        </is>
+      <c r="U16" s="7">
+        <f>"R2   "&amp;zn_FLM</f>
+        <v/>
       </c>
       <c r="AL16" s="19">
         <f>256-(COUNTA(B18:Q21)+COUNTA(B13:Q16)+COUNTA(B8:Q11)+COUNTA(U7:AJ10))</f>
         <v/>
       </c>
-      <c r="AN16" s="11" t="inlineStr">
-        <is>
-          <t>Boxes</t>
-        </is>
+      <c r="AN16" s="11">
+        <f>zn_BOX</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>L1   Boxes</t>
-        </is>
+      <c r="B17" s="7">
+        <f>"L1   "&amp;zn_BOX</f>
+        <v/>
       </c>
       <c r="U17" s="20" t="n"/>
       <c r="V17" s="20" t="n"/>
@@ -1349,10 +1364,9 @@
         <f>64-(COUNTA(U12:AJ15))</f>
         <v/>
       </c>
-      <c r="AN17" s="11" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
+      <c r="AN17" s="11">
+        <f>zn_BAG</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1392,10 +1406,9 @@
         <f>64-(COUNTA(U17:AJ20))</f>
         <v/>
       </c>
-      <c r="AN18" s="11" t="inlineStr">
-        <is>
-          <t>Films and Wrap</t>
-        </is>
+      <c r="AN18" s="11">
+        <f>zn_FLM</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1435,10 +1448,9 @@
         <f>32-(COUNTA(U22:AJ23))</f>
         <v/>
       </c>
-      <c r="AN19" s="11" t="inlineStr">
-        <is>
-          <t>Labels and Packing</t>
-        </is>
+      <c r="AN19" s="11">
+        <f>zn_LBL</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1492,10 +1504,9 @@
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n"/>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>R1   Labels and Packing</t>
-        </is>
+      <c r="U21" s="7">
+        <f>"R1   "&amp;zn_LBL</f>
+        <v/>
       </c>
       <c r="AL21" s="8" t="inlineStr">
         <is>
@@ -1883,25 +1894,25 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="B18:Q21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="L1  Boxes" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="B18:Q21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L1  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_BOX</formula1>
     </dataValidation>
-    <dataValidation sqref="B13:Q16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="L2  Boxes" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="B13:Q16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L2  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_BOX</formula1>
     </dataValidation>
-    <dataValidation sqref="B8:Q11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="L3  Boxes" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="B8:Q11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L3  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_BOX</formula1>
     </dataValidation>
-    <dataValidation sqref="U22:AJ23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="R1  Labels and Packing" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="U22:AJ23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle R1  (LBL)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_LBL</formula1>
     </dataValidation>
-    <dataValidation sqref="U17:AJ20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="R2  Films and Wrap" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="U17:AJ20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle R2  (FLM)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_FLM</formula1>
     </dataValidation>
-    <dataValidation sqref="U12:AJ15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="R3  Bags" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="U12:AJ15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle R3  (BAG)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_BAG</formula1>
     </dataValidation>
-    <dataValidation sqref="U7:AJ10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="R4  Boxes" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="U7:AJ10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle R4  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_BOX</formula1>
     </dataValidation>
   </dataValidations>
@@ -1917,7 +1928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1926,10 +1937,11 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1982,145 +1994,177 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Code</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>Zone name (you can change it)</t>
+        </is>
+      </c>
+      <c r="J4" s="27" t="inlineStr">
         <is>
           <t>Spaces</t>
         </is>
       </c>
-      <c r="J4" s="29" t="inlineStr">
+      <c r="K4" s="27" t="inlineStr">
         <is>
           <t>Used</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr">
+      <c r="L4" s="27" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>EX-BOX</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>EXAMPLE - type over me</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32">
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31">
         <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$28,tblStock[[#This Row],[Item code]]))</f>
         <v/>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <f>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
         <v/>
       </c>
-      <c r="H5" s="33" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>Boxes</t>
         </is>
       </c>
-      <c r="I5" s="34" t="n">
+      <c r="J5" s="31" t="n">
         <v>256</v>
       </c>
-      <c r="J5" s="34">
+      <c r="K5" s="31">
         <f>COUNTA(Map!B18:Q21)+COUNTA(Map!B13:Q16)+COUNTA(Map!B8:Q11)+COUNTA(Map!U7:AJ10)</f>
         <v/>
       </c>
-      <c r="K5" s="35">
-        <f>I5-J5</f>
+      <c r="L5" s="29">
+        <f>J5-K5</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>EX-WRAP</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>EXAMPLE - type over me</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>FLM</t>
         </is>
       </c>
-      <c r="D6" s="32" t="n"/>
-      <c r="E6" s="32">
+      <c r="D6" s="31" t="n"/>
+      <c r="E6" s="31">
         <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$28,tblStock[[#This Row],[Item code]]))</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <f>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
         <v/>
       </c>
-      <c r="H6" s="36" t="inlineStr">
+      <c r="H6" s="34" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>Bags</t>
         </is>
       </c>
-      <c r="I6" s="34" t="n">
+      <c r="J6" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="J6" s="34">
+      <c r="K6" s="31">
         <f>COUNTA(Map!U12:AJ15)</f>
         <v/>
       </c>
-      <c r="K6" s="35">
-        <f>I6-J6</f>
+      <c r="L6" s="29">
+        <f>J6-K6</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="H7" s="37" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>FLM</t>
+        </is>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>Films and Wrap</t>
         </is>
       </c>
-      <c r="I7" s="34" t="n">
+      <c r="J7" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="J7" s="34">
+      <c r="K7" s="31">
         <f>COUNTA(Map!U17:AJ20)</f>
         <v/>
       </c>
-      <c r="K7" s="35">
-        <f>I7-J7</f>
+      <c r="L7" s="29">
+        <f>J7-K7</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="H8" s="38" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>LBL</t>
+        </is>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>Labels and Packing</t>
         </is>
       </c>
-      <c r="I8" s="34" t="n">
+      <c r="J8" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="J8" s="34">
+      <c r="K8" s="31">
         <f>COUNTA(Map!U22:AJ23)</f>
         <v/>
       </c>
-      <c r="K8" s="35">
-        <f>I8-J8</f>
-        <v/>
+      <c r="L8" s="29">
+        <f>J8-K8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="37" t="inlineStr">
+        <is>
+          <t>Type over a zone name (pink box) and the Map changes too. In the Zone column on the left, use the Code.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Floor_Map_Simple.xlsx
+++ b/Floor_Map_Simple.xlsx
@@ -25,7 +25,7 @@
     <definedName name="dd_LBL">OFFSET(Lists!$E$3,0,0,MAX(1,Lists!$E$2),1)</definedName>
     <definedName name="ItemCodes">tblStock[Item code]</definedName>
     <definedName name="ItemZones">tblStock[Zone]</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Map'!$A$1:$AU$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Map'!$A$1:$AU$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -267,11 +267,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -298,14 +298,14 @@
     <xf numFmtId="0" fontId="13" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -513,7 +513,7 @@
     <tableColumn id="3" name="Zone"/>
     <tableColumn id="4" name="Low when pallets at or below"/>
     <tableColumn id="5" name="Pallets on map">
-      <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$28,tblStock[[#This Row],[Item code]]))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$27,tblStock[[#This Row],[Item code]]))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" name="Status">
       <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</calculatedColumnFormula>
@@ -813,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU30"/>
+  <dimension ref="A1:AU29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -969,12 +969,16 @@
     </row>
     <row r="5" ht="21" customHeight="1"/>
     <row r="6" ht="21" customHeight="1">
-      <c r="R6" s="6" t="inlineStr">
+      <c r="B6" s="6">
+        <f>"L3   "&amp;zn_BOX</f>
+        <v/>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t>WALKWAY</t>
         </is>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="6">
         <f>"R4   "&amp;zn_BOX</f>
         <v/>
       </c>
@@ -994,10 +998,22 @@
       <c r="AU6" s="5" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
-      <c r="B7" s="7">
-        <f>"L3   "&amp;zn_BOX</f>
-        <v/>
-      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
       <c r="U7" s="9" t="n"/>
       <c r="V7" s="9" t="n"/>
       <c r="W7" s="9" t="n"/>
@@ -1138,23 +1154,11 @@
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
-      <c r="O11" s="9" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="U11" s="7">
+      <c r="B11" s="6">
+        <f>"L2   "&amp;zn_BOX</f>
+        <v/>
+      </c>
+      <c r="U11" s="6">
         <f>"R3   "&amp;zn_BAG</f>
         <v/>
       </c>
@@ -1166,10 +1170,22 @@
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
-      <c r="B12" s="7">
-        <f>"L2   "&amp;zn_BOX</f>
-        <v/>
-      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="9" t="n"/>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
       <c r="U12" s="16" t="n"/>
       <c r="V12" s="16" t="n"/>
       <c r="W12" s="16" t="n"/>
@@ -1316,28 +1332,16 @@
       <c r="AU15" s="5" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
-      <c r="O16" s="9" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="9" t="n"/>
-      <c r="U16" s="7">
+      <c r="B16" s="6">
+        <f>"L1   "&amp;zn_BOX</f>
+        <v/>
+      </c>
+      <c r="U16" s="6">
         <f>"R2   "&amp;zn_FLM</f>
         <v/>
       </c>
       <c r="AL16" s="19">
-        <f>256-(COUNTA(B18:Q21)+COUNTA(B13:Q16)+COUNTA(B8:Q11)+COUNTA(U7:AJ10))</f>
+        <f>256-(COUNTA(B17:Q20)+COUNTA(B12:Q15)+COUNTA(B7:Q10)+COUNTA(U7:AJ10))</f>
         <v/>
       </c>
       <c r="AN16" s="11">
@@ -1346,10 +1350,22 @@
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="7">
-        <f>"L1   "&amp;zn_BOX</f>
-        <v/>
-      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
       <c r="U17" s="20" t="n"/>
       <c r="V17" s="20" t="n"/>
       <c r="W17" s="20" t="n"/>
@@ -1451,7 +1467,7 @@
       <c r="AI19" s="20" t="n"/>
       <c r="AJ19" s="20" t="n"/>
       <c r="AL19" s="19">
-        <f>32-(COUNTA(U22:AJ23))</f>
+        <f>16-(COUNTA(U22:AJ22))</f>
         <v/>
       </c>
       <c r="AN19" s="11">
@@ -1494,23 +1510,12 @@
       <c r="AJ20" s="20" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
-      <c r="O21" s="9" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="U21" s="7">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>XL   NOT OURS</t>
+        </is>
+      </c>
+      <c r="U21" s="6">
         <f>"R1   "&amp;zn_LBL</f>
         <v/>
       </c>
@@ -1530,28 +1535,43 @@
       <c r="AU21" s="5" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>XL   NOT OURS</t>
-        </is>
-      </c>
-      <c r="U22" s="21" t="n"/>
-      <c r="V22" s="21" t="n"/>
-      <c r="W22" s="21" t="n"/>
-      <c r="X22" s="21" t="n"/>
-      <c r="Y22" s="21" t="n"/>
-      <c r="Z22" s="21" t="n"/>
-      <c r="AA22" s="21" t="n"/>
-      <c r="AB22" s="21" t="n"/>
-      <c r="AC22" s="21" t="n"/>
-      <c r="AD22" s="21" t="n"/>
-      <c r="AE22" s="21" t="n"/>
-      <c r="AF22" s="21" t="n"/>
-      <c r="AG22" s="21" t="n"/>
-      <c r="AH22" s="21" t="n"/>
-      <c r="AI22" s="21" t="n"/>
-      <c r="AJ22" s="21" t="n"/>
-      <c r="AL22" s="22">
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>NOT OURS - someone else's space</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="18" t="n"/>
+      <c r="P22" s="18" t="n"/>
+      <c r="Q22" s="18" t="n"/>
+      <c r="U22" s="22" t="n"/>
+      <c r="V22" s="22" t="n"/>
+      <c r="W22" s="22" t="n"/>
+      <c r="X22" s="22" t="n"/>
+      <c r="Y22" s="22" t="n"/>
+      <c r="Z22" s="22" t="n"/>
+      <c r="AA22" s="22" t="n"/>
+      <c r="AB22" s="22" t="n"/>
+      <c r="AC22" s="22" t="n"/>
+      <c r="AD22" s="22" t="n"/>
+      <c r="AE22" s="22" t="n"/>
+      <c r="AF22" s="22" t="n"/>
+      <c r="AG22" s="22" t="n"/>
+      <c r="AH22" s="22" t="n"/>
+      <c r="AI22" s="22" t="n"/>
+      <c r="AJ22" s="22" t="n"/>
+      <c r="AL22" s="23">
         <f>COUNTIF(tblStock[Status],"LOW")</f>
         <v/>
       </c>
@@ -1562,11 +1582,7 @@
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>NOT OURS - someone else's space</t>
-        </is>
-      </c>
+      <c r="B23" s="18" t="n"/>
       <c r="C23" s="18" t="n"/>
       <c r="D23" s="18" t="n"/>
       <c r="E23" s="18" t="n"/>
@@ -1582,22 +1598,11 @@
       <c r="O23" s="18" t="n"/>
       <c r="P23" s="18" t="n"/>
       <c r="Q23" s="18" t="n"/>
-      <c r="U23" s="21" t="n"/>
-      <c r="V23" s="21" t="n"/>
-      <c r="W23" s="21" t="n"/>
-      <c r="X23" s="21" t="n"/>
-      <c r="Y23" s="21" t="n"/>
-      <c r="Z23" s="21" t="n"/>
-      <c r="AA23" s="21" t="n"/>
-      <c r="AB23" s="21" t="n"/>
-      <c r="AC23" s="21" t="n"/>
-      <c r="AD23" s="21" t="n"/>
-      <c r="AE23" s="21" t="n"/>
-      <c r="AF23" s="21" t="n"/>
-      <c r="AG23" s="21" t="n"/>
-      <c r="AH23" s="21" t="n"/>
-      <c r="AI23" s="21" t="n"/>
-      <c r="AJ23" s="21" t="n"/>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>XR   NOT OURS</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="B24" s="18" t="n"/>
@@ -1616,11 +1621,26 @@
       <c r="O24" s="18" t="n"/>
       <c r="P24" s="18" t="n"/>
       <c r="Q24" s="18" t="n"/>
-      <c r="U24" s="7" t="inlineStr">
-        <is>
-          <t>XR   NOT OURS</t>
-        </is>
-      </c>
+      <c r="U24" s="21" t="inlineStr">
+        <is>
+          <t>NOT OURS - someone else's space</t>
+        </is>
+      </c>
+      <c r="V24" s="18" t="n"/>
+      <c r="W24" s="18" t="n"/>
+      <c r="X24" s="18" t="n"/>
+      <c r="Y24" s="18" t="n"/>
+      <c r="Z24" s="18" t="n"/>
+      <c r="AA24" s="18" t="n"/>
+      <c r="AB24" s="18" t="n"/>
+      <c r="AC24" s="18" t="n"/>
+      <c r="AD24" s="18" t="n"/>
+      <c r="AE24" s="18" t="n"/>
+      <c r="AF24" s="18" t="n"/>
+      <c r="AG24" s="18" t="n"/>
+      <c r="AH24" s="18" t="n"/>
+      <c r="AI24" s="18" t="n"/>
+      <c r="AJ24" s="18" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="B25" s="18" t="n"/>
@@ -1639,11 +1659,7 @@
       <c r="O25" s="18" t="n"/>
       <c r="P25" s="18" t="n"/>
       <c r="Q25" s="18" t="n"/>
-      <c r="U25" s="23" t="inlineStr">
-        <is>
-          <t>NOT OURS - someone else's space</t>
-        </is>
-      </c>
+      <c r="U25" s="18" t="n"/>
       <c r="V25" s="18" t="n"/>
       <c r="W25" s="18" t="n"/>
       <c r="X25" s="18" t="n"/>
@@ -1728,146 +1744,112 @@
       <c r="AI27" s="18" t="n"/>
       <c r="AJ27" s="18" t="n"/>
     </row>
-    <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="18" t="n"/>
-      <c r="I28" s="18" t="n"/>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="18" t="n"/>
-      <c r="L28" s="18" t="n"/>
-      <c r="M28" s="18" t="n"/>
-      <c r="N28" s="18" t="n"/>
-      <c r="O28" s="18" t="n"/>
-      <c r="P28" s="18" t="n"/>
-      <c r="Q28" s="18" t="n"/>
-      <c r="U28" s="18" t="n"/>
-      <c r="V28" s="18" t="n"/>
-      <c r="W28" s="18" t="n"/>
-      <c r="X28" s="18" t="n"/>
-      <c r="Y28" s="18" t="n"/>
-      <c r="Z28" s="18" t="n"/>
-      <c r="AA28" s="18" t="n"/>
-      <c r="AB28" s="18" t="n"/>
-      <c r="AC28" s="18" t="n"/>
-      <c r="AD28" s="18" t="n"/>
-      <c r="AE28" s="18" t="n"/>
-      <c r="AF28" s="18" t="n"/>
-      <c r="AG28" s="18" t="n"/>
-      <c r="AH28" s="18" t="n"/>
-      <c r="AI28" s="18" t="n"/>
-      <c r="AJ28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="21" customHeight="1"/>
-    <row r="30" ht="21" customHeight="1">
-      <c r="B30" s="24" t="inlineStr">
+    <row r="28" ht="21" customHeight="1"/>
+    <row r="29" ht="21" customHeight="1">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>FIRE EXIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="25" t="n"/>
-      <c r="L30" s="25" t="n"/>
-      <c r="M30" s="25" t="n"/>
-      <c r="N30" s="25" t="n"/>
-      <c r="O30" s="25" t="n"/>
-      <c r="P30" s="25" t="n"/>
-      <c r="Q30" s="25" t="n"/>
-      <c r="R30" s="25" t="n"/>
-      <c r="S30" s="25" t="n"/>
-      <c r="T30" s="25" t="n"/>
-      <c r="U30" s="25" t="n"/>
-      <c r="V30" s="25" t="n"/>
-      <c r="W30" s="25" t="n"/>
-      <c r="X30" s="25" t="n"/>
-      <c r="Y30" s="25" t="n"/>
-      <c r="Z30" s="25" t="n"/>
-      <c r="AA30" s="25" t="n"/>
-      <c r="AB30" s="25" t="n"/>
-      <c r="AC30" s="25" t="n"/>
-      <c r="AD30" s="25" t="n"/>
-      <c r="AE30" s="25" t="n"/>
-      <c r="AF30" s="25" t="n"/>
-      <c r="AG30" s="25" t="n"/>
-      <c r="AH30" s="25" t="n"/>
-      <c r="AI30" s="25" t="n"/>
-      <c r="AJ30" s="25" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="25" t="n"/>
+      <c r="L29" s="25" t="n"/>
+      <c r="M29" s="25" t="n"/>
+      <c r="N29" s="25" t="n"/>
+      <c r="O29" s="25" t="n"/>
+      <c r="P29" s="25" t="n"/>
+      <c r="Q29" s="25" t="n"/>
+      <c r="R29" s="25" t="n"/>
+      <c r="S29" s="25" t="n"/>
+      <c r="T29" s="25" t="n"/>
+      <c r="U29" s="25" t="n"/>
+      <c r="V29" s="25" t="n"/>
+      <c r="W29" s="25" t="n"/>
+      <c r="X29" s="25" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="25" t="n"/>
+      <c r="AA29" s="25" t="n"/>
+      <c r="AB29" s="25" t="n"/>
+      <c r="AC29" s="25" t="n"/>
+      <c r="AD29" s="25" t="n"/>
+      <c r="AE29" s="25" t="n"/>
+      <c r="AF29" s="25" t="n"/>
+      <c r="AG29" s="25" t="n"/>
+      <c r="AH29" s="25" t="n"/>
+      <c r="AI29" s="25" t="n"/>
+      <c r="AJ29" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="R6:T28"/>
     <mergeCell ref="AN13:AU13"/>
-    <mergeCell ref="U24:AJ24"/>
     <mergeCell ref="AN9:AU9"/>
     <mergeCell ref="B4:AJ4"/>
+    <mergeCell ref="B22:Q27"/>
+    <mergeCell ref="B6:Q6"/>
+    <mergeCell ref="U23:AJ23"/>
+    <mergeCell ref="R6:T27"/>
     <mergeCell ref="AL16:AM16"/>
     <mergeCell ref="AL22:AM22"/>
     <mergeCell ref="AN16:AU16"/>
     <mergeCell ref="A1:AU1"/>
+    <mergeCell ref="B16:Q16"/>
     <mergeCell ref="AL6:AU6"/>
-    <mergeCell ref="B7:Q7"/>
     <mergeCell ref="AL15:AU15"/>
     <mergeCell ref="U6:AJ6"/>
-    <mergeCell ref="U25:AJ28"/>
+    <mergeCell ref="AN22:AU22"/>
     <mergeCell ref="AL18:AM18"/>
-    <mergeCell ref="B22:Q22"/>
-    <mergeCell ref="AN22:AU22"/>
-    <mergeCell ref="B23:Q28"/>
     <mergeCell ref="AN12:AU12"/>
-    <mergeCell ref="B12:Q12"/>
+    <mergeCell ref="B21:Q21"/>
     <mergeCell ref="AN11:AU11"/>
     <mergeCell ref="AN18:AU18"/>
+    <mergeCell ref="B11:Q11"/>
+    <mergeCell ref="B29:AJ29"/>
     <mergeCell ref="AL17:AM17"/>
     <mergeCell ref="U11:AJ11"/>
+    <mergeCell ref="U24:AJ27"/>
     <mergeCell ref="A2:AU2"/>
     <mergeCell ref="U16:AJ16"/>
     <mergeCell ref="AN8:AU8"/>
     <mergeCell ref="AN17:AU17"/>
-    <mergeCell ref="B17:Q17"/>
     <mergeCell ref="AN7:AU7"/>
     <mergeCell ref="AL19:AM19"/>
     <mergeCell ref="AL21:AU21"/>
     <mergeCell ref="AN10:AU10"/>
-    <mergeCell ref="B30:AJ30"/>
     <mergeCell ref="AN19:AU19"/>
     <mergeCell ref="U21:AJ21"/>
   </mergeCells>
-  <conditionalFormatting sqref="B18:Q21">
+  <conditionalFormatting sqref="B17:Q20">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>AND(LEN(B18)&gt;0,IFERROR(INDEX(ItemZones,MATCH(B18,ItemCodes,0)),"BOX")&lt;&gt;"BOX")</formula>
+      <formula>AND(LEN(B17)&gt;0,IFERROR(INDEX(ItemZones,MATCH(B17,ItemCodes,0)),"BOX")&lt;&gt;"BOX")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>LEN(B18)&gt;0</formula>
+      <formula>LEN(B17)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:Q16">
+  <conditionalFormatting sqref="B12:Q15">
     <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
-      <formula>AND(LEN(B13)&gt;0,IFERROR(INDEX(ItemZones,MATCH(B13,ItemCodes,0)),"BOX")&lt;&gt;"BOX")</formula>
+      <formula>AND(LEN(B12)&gt;0,IFERROR(INDEX(ItemZones,MATCH(B12,ItemCodes,0)),"BOX")&lt;&gt;"BOX")</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>LEN(B13)&gt;0</formula>
+      <formula>LEN(B12)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:Q11">
+  <conditionalFormatting sqref="B7:Q10">
     <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="1">
-      <formula>AND(LEN(B8)&gt;0,IFERROR(INDEX(ItemZones,MATCH(B8,ItemCodes,0)),"BOX")&lt;&gt;"BOX")</formula>
+      <formula>AND(LEN(B7)&gt;0,IFERROR(INDEX(ItemZones,MATCH(B7,ItemCodes,0)),"BOX")&lt;&gt;"BOX")</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>LEN(B8)&gt;0</formula>
+      <formula>LEN(B7)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U22:AJ23">
+  <conditionalFormatting sqref="U22:AJ22">
     <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
       <formula>AND(LEN(U22)&gt;0,IFERROR(INDEX(ItemZones,MATCH(U22,ItemCodes,0)),"LBL")&lt;&gt;"LBL")</formula>
     </cfRule>
@@ -1900,16 +1882,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="B18:Q21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L1  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="B17:Q20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L1  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_BOX</formula1>
     </dataValidation>
-    <dataValidation sqref="B13:Q16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L2  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="B12:Q15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L2  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_BOX</formula1>
     </dataValidation>
-    <dataValidation sqref="B8:Q11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L3  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="B7:Q10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle L3  (BOX)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_BOX</formula1>
     </dataValidation>
-    <dataValidation sqref="U22:AJ23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle R1  (LBL)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
+    <dataValidation sqref="U22:AJ22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle R1  (LBL)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
       <formula1>dd_LBL</formula1>
     </dataValidation>
     <dataValidation sqref="U17:AJ20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not for this zone" error="That item isn't listed for this zone (or isn't on the Stock sheet). Put it here anyway?" promptTitle="Aisle R2  (FLM)" prompt="Click the arrow and pick an item. Press Delete to empty." type="list" errorStyle="warning">
@@ -2044,7 +2026,7 @@
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31">
-        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$28,tblStock[[#This Row],[Item code]]))</f>
+        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$27,tblStock[[#This Row],[Item code]]))</f>
         <v/>
       </c>
       <c r="F5" s="29">
@@ -2065,7 +2047,7 @@
         <v>256</v>
       </c>
       <c r="K5" s="31">
-        <f>COUNTA(Map!B18:Q21)+COUNTA(Map!B13:Q16)+COUNTA(Map!B8:Q11)+COUNTA(Map!U7:AJ10)</f>
+        <f>COUNTA(Map!B17:Q20)+COUNTA(Map!B12:Q15)+COUNTA(Map!B7:Q10)+COUNTA(Map!U7:AJ10)</f>
         <v/>
       </c>
       <c r="L5" s="29">
@@ -2091,7 +2073,7 @@
       </c>
       <c r="D6" s="31" t="n"/>
       <c r="E6" s="31">
-        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$28,tblStock[[#This Row],[Item code]]))</f>
+        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$27,tblStock[[#This Row],[Item code]]))</f>
         <v/>
       </c>
       <c r="F6" s="29">
@@ -2155,10 +2137,10 @@
         </is>
       </c>
       <c r="J8" s="31" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K8" s="31">
-        <f>COUNTA(Map!U22:AJ23)</f>
+        <f>COUNTA(Map!U22:AJ22)</f>
         <v/>
       </c>
       <c r="L8" s="29">
@@ -5644,7 +5626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F417"/>
+  <dimension ref="A1:F401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5696,7 +5678,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
@@ -5722,7 +5704,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
         <v>16</v>
@@ -5748,7 +5730,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
         <v>15</v>
@@ -5774,7 +5756,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
         <v>14</v>
@@ -5800,7 +5782,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>13</v>
@@ -5826,7 +5808,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
@@ -5852,7 +5834,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
         <v>11</v>
@@ -5878,7 +5860,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
@@ -5904,7 +5886,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -5930,7 +5912,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>
@@ -5956,7 +5938,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
@@ -5982,7 +5964,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>6</v>
@@ -6008,7 +5990,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
@@ -6034,7 +6016,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -6060,7 +6042,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -6086,7 +6068,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -6112,7 +6094,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -6138,7 +6120,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
@@ -6164,7 +6146,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
@@ -6190,7 +6172,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
@@ -6216,7 +6198,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
         <v>13</v>
@@ -6242,7 +6224,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
@@ -6268,7 +6250,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
         <v>11</v>
@@ -6294,7 +6276,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
         <v>10</v>
@@ -6320,7 +6302,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
         <v>9</v>
@@ -6346,7 +6328,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
         <v>8</v>
@@ -6372,7 +6354,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>7</v>
@@ -6398,7 +6380,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
         <v>6</v>
@@ -6424,7 +6406,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
         <v>5</v>
@@ -6450,7 +6432,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
@@ -6476,7 +6458,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
@@ -6502,7 +6484,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
@@ -6528,7 +6510,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" t="n">
         <v>17</v>
@@ -6554,7 +6536,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
         <v>16</v>
@@ -6580,7 +6562,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
         <v>15</v>
@@ -6606,7 +6588,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" t="n">
         <v>14</v>
@@ -6632,7 +6614,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E38" t="n">
         <v>13</v>
@@ -6658,7 +6640,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
         <v>12</v>
@@ -6684,7 +6666,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E40" t="n">
         <v>11</v>
@@ -6710,7 +6692,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E41" t="n">
         <v>10</v>
@@ -6736,7 +6718,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E42" t="n">
         <v>9</v>
@@ -6762,7 +6744,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" t="n">
         <v>8</v>
@@ -6788,7 +6770,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E44" t="n">
         <v>7</v>
@@ -6814,7 +6796,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E45" t="n">
         <v>6</v>
@@ -6840,7 +6822,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46" t="n">
         <v>5</v>
@@ -6866,7 +6848,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
         <v>4</v>
@@ -6892,7 +6874,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
@@ -6918,7 +6900,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -6944,7 +6926,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
         <v>17</v>
@@ -6970,7 +6952,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E51" t="n">
         <v>16</v>
@@ -6996,7 +6978,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E52" t="n">
         <v>15</v>
@@ -7022,7 +7004,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E53" t="n">
         <v>14</v>
@@ -7048,7 +7030,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E54" t="n">
         <v>13</v>
@@ -7074,7 +7056,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E55" t="n">
         <v>12</v>
@@ -7100,7 +7082,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E56" t="n">
         <v>11</v>
@@ -7126,7 +7108,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E57" t="n">
         <v>10</v>
@@ -7152,7 +7134,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E58" t="n">
         <v>9</v>
@@ -7178,7 +7160,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E59" t="n">
         <v>8</v>
@@ -7204,7 +7186,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E60" t="n">
         <v>7</v>
@@ -7230,7 +7212,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E61" t="n">
         <v>6</v>
@@ -7256,7 +7238,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E62" t="n">
         <v>5</v>
@@ -7282,7 +7264,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E63" t="n">
         <v>4</v>
@@ -7308,7 +7290,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E64" t="n">
         <v>3</v>
@@ -7334,7 +7316,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
@@ -7360,7 +7342,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E66" t="n">
         <v>17</v>
@@ -7386,7 +7368,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E67" t="n">
         <v>16</v>
@@ -7412,7 +7394,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E68" t="n">
         <v>15</v>
@@ -7438,7 +7420,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E69" t="n">
         <v>14</v>
@@ -7464,7 +7446,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E70" t="n">
         <v>13</v>
@@ -7490,7 +7472,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
         <v>12</v>
@@ -7516,7 +7498,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E72" t="n">
         <v>11</v>
@@ -7542,7 +7524,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
         <v>10</v>
@@ -7568,7 +7550,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E74" t="n">
         <v>9</v>
@@ -7594,7 +7576,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E75" t="n">
         <v>8</v>
@@ -7620,7 +7602,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E76" t="n">
         <v>7</v>
@@ -7646,7 +7628,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E77" t="n">
         <v>6</v>
@@ -7672,7 +7654,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
         <v>5</v>
@@ -7698,7 +7680,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E79" t="n">
         <v>4</v>
@@ -7724,7 +7706,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E80" t="n">
         <v>3</v>
@@ -7750,7 +7732,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -7776,7 +7758,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E82" t="n">
         <v>17</v>
@@ -7802,7 +7784,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E83" t="n">
         <v>16</v>
@@ -7828,7 +7810,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E84" t="n">
         <v>15</v>
@@ -7854,7 +7836,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E85" t="n">
         <v>14</v>
@@ -7880,7 +7862,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E86" t="n">
         <v>13</v>
@@ -7906,7 +7888,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E87" t="n">
         <v>12</v>
@@ -7932,7 +7914,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E88" t="n">
         <v>11</v>
@@ -7958,7 +7940,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E89" t="n">
         <v>10</v>
@@ -7984,7 +7966,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E90" t="n">
         <v>9</v>
@@ -8010,7 +7992,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E91" t="n">
         <v>8</v>
@@ -8036,7 +8018,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E92" t="n">
         <v>7</v>
@@ -8062,7 +8044,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E93" t="n">
         <v>6</v>
@@ -8088,7 +8070,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E94" t="n">
         <v>5</v>
@@ -8114,7 +8096,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E95" t="n">
         <v>4</v>
@@ -8140,7 +8122,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E96" t="n">
         <v>3</v>
@@ -8166,7 +8148,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E97" t="n">
         <v>2</v>
@@ -8192,7 +8174,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E98" t="n">
         <v>17</v>
@@ -8218,7 +8200,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E99" t="n">
         <v>16</v>
@@ -8244,7 +8226,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E100" t="n">
         <v>15</v>
@@ -8270,7 +8252,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E101" t="n">
         <v>14</v>
@@ -8296,7 +8278,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E102" t="n">
         <v>13</v>
@@ -8322,7 +8304,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E103" t="n">
         <v>12</v>
@@ -8348,7 +8330,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E104" t="n">
         <v>11</v>
@@ -8374,7 +8356,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E105" t="n">
         <v>10</v>
@@ -8400,7 +8382,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E106" t="n">
         <v>9</v>
@@ -8426,7 +8408,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E107" t="n">
         <v>8</v>
@@ -8452,7 +8434,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E108" t="n">
         <v>7</v>
@@ -8478,7 +8460,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E109" t="n">
         <v>6</v>
@@ -8504,7 +8486,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E110" t="n">
         <v>5</v>
@@ -8530,7 +8512,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E111" t="n">
         <v>4</v>
@@ -8556,7 +8538,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E112" t="n">
         <v>3</v>
@@ -8582,7 +8564,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -8608,7 +8590,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E114" t="n">
         <v>17</v>
@@ -8634,7 +8616,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E115" t="n">
         <v>16</v>
@@ -8660,7 +8642,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E116" t="n">
         <v>15</v>
@@ -8686,7 +8668,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E117" t="n">
         <v>14</v>
@@ -8712,7 +8694,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E118" t="n">
         <v>13</v>
@@ -8738,7 +8720,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E119" t="n">
         <v>12</v>
@@ -8764,7 +8746,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E120" t="n">
         <v>11</v>
@@ -8790,7 +8772,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E121" t="n">
         <v>10</v>
@@ -8816,7 +8798,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E122" t="n">
         <v>9</v>
@@ -8842,7 +8824,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E123" t="n">
         <v>8</v>
@@ -8868,7 +8850,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E124" t="n">
         <v>7</v>
@@ -8894,7 +8876,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E125" t="n">
         <v>6</v>
@@ -8920,7 +8902,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E126" t="n">
         <v>5</v>
@@ -8946,7 +8928,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E127" t="n">
         <v>4</v>
@@ -8972,7 +8954,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E128" t="n">
         <v>3</v>
@@ -8998,7 +8980,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E129" t="n">
         <v>2</v>
@@ -9024,7 +9006,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E130" t="n">
         <v>17</v>
@@ -9050,7 +9032,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E131" t="n">
         <v>16</v>
@@ -9076,7 +9058,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E132" t="n">
         <v>15</v>
@@ -9102,7 +9084,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E133" t="n">
         <v>14</v>
@@ -9128,7 +9110,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E134" t="n">
         <v>13</v>
@@ -9154,7 +9136,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E135" t="n">
         <v>12</v>
@@ -9180,7 +9162,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E136" t="n">
         <v>11</v>
@@ -9206,7 +9188,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E137" t="n">
         <v>10</v>
@@ -9232,7 +9214,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E138" t="n">
         <v>9</v>
@@ -9258,7 +9240,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E139" t="n">
         <v>8</v>
@@ -9284,7 +9266,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E140" t="n">
         <v>7</v>
@@ -9310,7 +9292,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E141" t="n">
         <v>6</v>
@@ -9336,7 +9318,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E142" t="n">
         <v>5</v>
@@ -9362,7 +9344,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E143" t="n">
         <v>4</v>
@@ -9388,7 +9370,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E144" t="n">
         <v>3</v>
@@ -9414,7 +9396,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -9440,7 +9422,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E146" t="n">
         <v>17</v>
@@ -9466,7 +9448,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E147" t="n">
         <v>16</v>
@@ -9492,7 +9474,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E148" t="n">
         <v>15</v>
@@ -9518,7 +9500,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E149" t="n">
         <v>14</v>
@@ -9544,7 +9526,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E150" t="n">
         <v>13</v>
@@ -9570,7 +9552,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E151" t="n">
         <v>12</v>
@@ -9596,7 +9578,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E152" t="n">
         <v>11</v>
@@ -9622,7 +9604,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E153" t="n">
         <v>10</v>
@@ -9648,7 +9630,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E154" t="n">
         <v>9</v>
@@ -9674,7 +9656,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E155" t="n">
         <v>8</v>
@@ -9700,7 +9682,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E156" t="n">
         <v>7</v>
@@ -9726,7 +9708,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E157" t="n">
         <v>6</v>
@@ -9752,7 +9734,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E158" t="n">
         <v>5</v>
@@ -9778,7 +9760,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E159" t="n">
         <v>4</v>
@@ -9804,7 +9786,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E160" t="n">
         <v>3</v>
@@ -9830,7 +9812,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E161" t="n">
         <v>2</v>
@@ -9856,7 +9838,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E162" t="n">
         <v>17</v>
@@ -9882,7 +9864,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E163" t="n">
         <v>16</v>
@@ -9908,7 +9890,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E164" t="n">
         <v>15</v>
@@ -9934,7 +9916,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E165" t="n">
         <v>14</v>
@@ -9960,7 +9942,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E166" t="n">
         <v>13</v>
@@ -9986,7 +9968,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E167" t="n">
         <v>12</v>
@@ -10012,7 +9994,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E168" t="n">
         <v>11</v>
@@ -10038,7 +10020,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E169" t="n">
         <v>10</v>
@@ -10064,7 +10046,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E170" t="n">
         <v>9</v>
@@ -10090,7 +10072,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E171" t="n">
         <v>8</v>
@@ -10116,7 +10098,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E172" t="n">
         <v>7</v>
@@ -10142,7 +10124,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E173" t="n">
         <v>6</v>
@@ -10168,7 +10150,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E174" t="n">
         <v>5</v>
@@ -10194,7 +10176,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E175" t="n">
         <v>4</v>
@@ -10220,7 +10202,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E176" t="n">
         <v>3</v>
@@ -10246,7 +10228,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E177" t="n">
         <v>2</v>
@@ -10272,7 +10254,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E178" t="n">
         <v>17</v>
@@ -10298,7 +10280,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E179" t="n">
         <v>16</v>
@@ -10324,7 +10306,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E180" t="n">
         <v>15</v>
@@ -10350,7 +10332,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E181" t="n">
         <v>14</v>
@@ -10376,7 +10358,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E182" t="n">
         <v>13</v>
@@ -10402,7 +10384,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E183" t="n">
         <v>12</v>
@@ -10428,7 +10410,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E184" t="n">
         <v>11</v>
@@ -10454,7 +10436,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E185" t="n">
         <v>10</v>
@@ -10480,7 +10462,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E186" t="n">
         <v>9</v>
@@ -10506,7 +10488,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E187" t="n">
         <v>8</v>
@@ -10532,7 +10514,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E188" t="n">
         <v>7</v>
@@ -10558,7 +10540,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E189" t="n">
         <v>6</v>
@@ -10584,7 +10566,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E190" t="n">
         <v>5</v>
@@ -10610,7 +10592,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E191" t="n">
         <v>4</v>
@@ -10636,7 +10618,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E192" t="n">
         <v>3</v>
@@ -10662,7 +10644,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E193" t="n">
         <v>2</v>
@@ -11090,21 +11072,21 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>R1-01-B</t>
+          <t>R2-01-A</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E210" t="n">
         <v>21</v>
@@ -11116,21 +11098,21 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>R1-02-B</t>
+          <t>R2-02-A</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E211" t="n">
         <v>22</v>
@@ -11142,21 +11124,21 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>R1-03-B</t>
+          <t>R2-03-A</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E212" t="n">
         <v>23</v>
@@ -11168,21 +11150,21 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>R1-04-B</t>
+          <t>R2-04-A</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E213" t="n">
         <v>24</v>
@@ -11194,21 +11176,21 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>R1-05-B</t>
+          <t>R2-05-A</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E214" t="n">
         <v>25</v>
@@ -11220,21 +11202,21 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>R1-06-B</t>
+          <t>R2-06-A</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E215" t="n">
         <v>26</v>
@@ -11246,21 +11228,21 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>R1-07-B</t>
+          <t>R2-07-A</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E216" t="n">
         <v>27</v>
@@ -11272,21 +11254,21 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>R1-08-B</t>
+          <t>R2-08-A</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E217" t="n">
         <v>28</v>
@@ -11298,21 +11280,21 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>R1-09-B</t>
+          <t>R2-09-A</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E218" t="n">
         <v>29</v>
@@ -11324,21 +11306,21 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>R1-10-B</t>
+          <t>R2-10-A</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E219" t="n">
         <v>30</v>
@@ -11350,21 +11332,21 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>R1-11-B</t>
+          <t>R2-11-A</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E220" t="n">
         <v>31</v>
@@ -11376,21 +11358,21 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>R1-12-B</t>
+          <t>R2-12-A</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E221" t="n">
         <v>32</v>
@@ -11402,21 +11384,21 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>R1-13-B</t>
+          <t>R2-13-A</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E222" t="n">
         <v>33</v>
@@ -11428,21 +11410,21 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>R1-14-B</t>
+          <t>R2-14-A</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E223" t="n">
         <v>34</v>
@@ -11454,21 +11436,21 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>R1-15-B</t>
+          <t>R2-15-A</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E224" t="n">
         <v>35</v>
@@ -11480,21 +11462,21 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>R1-16-B</t>
+          <t>R2-16-A</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E225" t="n">
         <v>36</v>
@@ -11506,7 +11488,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>R2-01-A</t>
+          <t>R2-01-B</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11520,7 +11502,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E226" t="n">
         <v>21</v>
@@ -11532,7 +11514,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>R2-02-A</t>
+          <t>R2-02-B</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -11546,7 +11528,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E227" t="n">
         <v>22</v>
@@ -11558,7 +11540,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>R2-03-A</t>
+          <t>R2-03-B</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -11572,7 +11554,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E228" t="n">
         <v>23</v>
@@ -11584,7 +11566,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>R2-04-A</t>
+          <t>R2-04-B</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -11598,7 +11580,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E229" t="n">
         <v>24</v>
@@ -11610,7 +11592,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>R2-05-A</t>
+          <t>R2-05-B</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -11624,7 +11606,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E230" t="n">
         <v>25</v>
@@ -11636,7 +11618,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>R2-06-A</t>
+          <t>R2-06-B</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -11650,7 +11632,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E231" t="n">
         <v>26</v>
@@ -11662,7 +11644,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>R2-07-A</t>
+          <t>R2-07-B</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -11676,7 +11658,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E232" t="n">
         <v>27</v>
@@ -11688,7 +11670,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>R2-08-A</t>
+          <t>R2-08-B</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -11702,7 +11684,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E233" t="n">
         <v>28</v>
@@ -11714,7 +11696,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>R2-09-A</t>
+          <t>R2-09-B</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -11728,7 +11710,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E234" t="n">
         <v>29</v>
@@ -11740,7 +11722,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>R2-10-A</t>
+          <t>R2-10-B</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -11754,7 +11736,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E235" t="n">
         <v>30</v>
@@ -11766,7 +11748,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>R2-11-A</t>
+          <t>R2-11-B</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -11780,7 +11762,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E236" t="n">
         <v>31</v>
@@ -11792,7 +11774,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>R2-12-A</t>
+          <t>R2-12-B</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -11806,7 +11788,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E237" t="n">
         <v>32</v>
@@ -11818,7 +11800,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>R2-13-A</t>
+          <t>R2-13-B</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -11832,7 +11814,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E238" t="n">
         <v>33</v>
@@ -11844,7 +11826,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>R2-14-A</t>
+          <t>R2-14-B</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -11858,7 +11840,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E239" t="n">
         <v>34</v>
@@ -11870,7 +11852,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>R2-15-A</t>
+          <t>R2-15-B</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -11884,7 +11866,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E240" t="n">
         <v>35</v>
@@ -11896,7 +11878,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>R2-16-A</t>
+          <t>R2-16-B</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -11910,7 +11892,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E241" t="n">
         <v>36</v>
@@ -11922,7 +11904,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>R2-01-B</t>
+          <t>R2-01-C</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -11936,7 +11918,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E242" t="n">
         <v>21</v>
@@ -11948,7 +11930,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>R2-02-B</t>
+          <t>R2-02-C</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -11962,7 +11944,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E243" t="n">
         <v>22</v>
@@ -11974,7 +11956,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>R2-03-B</t>
+          <t>R2-03-C</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -11988,7 +11970,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E244" t="n">
         <v>23</v>
@@ -12000,7 +11982,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>R2-04-B</t>
+          <t>R2-04-C</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12014,7 +11996,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E245" t="n">
         <v>24</v>
@@ -12026,7 +12008,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>R2-05-B</t>
+          <t>R2-05-C</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12040,7 +12022,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E246" t="n">
         <v>25</v>
@@ -12052,7 +12034,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>R2-06-B</t>
+          <t>R2-06-C</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12066,7 +12048,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E247" t="n">
         <v>26</v>
@@ -12078,7 +12060,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>R2-07-B</t>
+          <t>R2-07-C</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12092,7 +12074,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E248" t="n">
         <v>27</v>
@@ -12104,7 +12086,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>R2-08-B</t>
+          <t>R2-08-C</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12118,7 +12100,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E249" t="n">
         <v>28</v>
@@ -12130,7 +12112,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>R2-09-B</t>
+          <t>R2-09-C</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12144,7 +12126,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E250" t="n">
         <v>29</v>
@@ -12156,7 +12138,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>R2-10-B</t>
+          <t>R2-10-C</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12170,7 +12152,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E251" t="n">
         <v>30</v>
@@ -12182,7 +12164,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>R2-11-B</t>
+          <t>R2-11-C</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12196,7 +12178,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E252" t="n">
         <v>31</v>
@@ -12208,7 +12190,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>R2-12-B</t>
+          <t>R2-12-C</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12222,7 +12204,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E253" t="n">
         <v>32</v>
@@ -12234,7 +12216,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>R2-13-B</t>
+          <t>R2-13-C</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12248,7 +12230,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E254" t="n">
         <v>33</v>
@@ -12260,7 +12242,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>R2-14-B</t>
+          <t>R2-14-C</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12274,7 +12256,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E255" t="n">
         <v>34</v>
@@ -12286,7 +12268,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>R2-15-B</t>
+          <t>R2-15-C</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12300,7 +12282,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E256" t="n">
         <v>35</v>
@@ -12312,7 +12294,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>R2-16-B</t>
+          <t>R2-16-C</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -12326,7 +12308,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E257" t="n">
         <v>36</v>
@@ -12338,7 +12320,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>R2-01-C</t>
+          <t>R2-01-D</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -12352,7 +12334,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E258" t="n">
         <v>21</v>
@@ -12364,7 +12346,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>R2-02-C</t>
+          <t>R2-02-D</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -12378,7 +12360,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E259" t="n">
         <v>22</v>
@@ -12390,7 +12372,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>R2-03-C</t>
+          <t>R2-03-D</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -12404,7 +12386,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E260" t="n">
         <v>23</v>
@@ -12416,7 +12398,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>R2-04-C</t>
+          <t>R2-04-D</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -12430,7 +12412,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E261" t="n">
         <v>24</v>
@@ -12442,7 +12424,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>R2-05-C</t>
+          <t>R2-05-D</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -12456,7 +12438,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E262" t="n">
         <v>25</v>
@@ -12468,7 +12450,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>R2-06-C</t>
+          <t>R2-06-D</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12482,7 +12464,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E263" t="n">
         <v>26</v>
@@ -12494,7 +12476,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>R2-07-C</t>
+          <t>R2-07-D</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -12508,7 +12490,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E264" t="n">
         <v>27</v>
@@ -12520,7 +12502,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>R2-08-C</t>
+          <t>R2-08-D</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12534,7 +12516,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E265" t="n">
         <v>28</v>
@@ -12546,7 +12528,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>R2-09-C</t>
+          <t>R2-09-D</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -12560,7 +12542,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E266" t="n">
         <v>29</v>
@@ -12572,7 +12554,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>R2-10-C</t>
+          <t>R2-10-D</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12586,7 +12568,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E267" t="n">
         <v>30</v>
@@ -12598,7 +12580,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>R2-11-C</t>
+          <t>R2-11-D</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -12612,7 +12594,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E268" t="n">
         <v>31</v>
@@ -12624,7 +12606,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>R2-12-C</t>
+          <t>R2-12-D</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12638,7 +12620,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E269" t="n">
         <v>32</v>
@@ -12650,7 +12632,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>R2-13-C</t>
+          <t>R2-13-D</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -12664,7 +12646,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E270" t="n">
         <v>33</v>
@@ -12676,7 +12658,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>R2-14-C</t>
+          <t>R2-14-D</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12690,7 +12672,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E271" t="n">
         <v>34</v>
@@ -12702,7 +12684,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>R2-15-C</t>
+          <t>R2-15-D</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -12716,7 +12698,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E272" t="n">
         <v>35</v>
@@ -12728,7 +12710,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>R2-16-C</t>
+          <t>R2-16-D</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12742,7 +12724,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E273" t="n">
         <v>36</v>
@@ -12754,21 +12736,21 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>R2-01-D</t>
+          <t>R3-01-A</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E274" t="n">
         <v>21</v>
@@ -12780,21 +12762,21 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>R2-02-D</t>
+          <t>R3-02-A</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E275" t="n">
         <v>22</v>
@@ -12806,21 +12788,21 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>R2-03-D</t>
+          <t>R3-03-A</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E276" t="n">
         <v>23</v>
@@ -12832,21 +12814,21 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>R2-04-D</t>
+          <t>R3-04-A</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E277" t="n">
         <v>24</v>
@@ -12858,21 +12840,21 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>R2-05-D</t>
+          <t>R3-05-A</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E278" t="n">
         <v>25</v>
@@ -12884,21 +12866,21 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>R2-06-D</t>
+          <t>R3-06-A</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E279" t="n">
         <v>26</v>
@@ -12910,21 +12892,21 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>R2-07-D</t>
+          <t>R3-07-A</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E280" t="n">
         <v>27</v>
@@ -12936,21 +12918,21 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>R2-08-D</t>
+          <t>R3-08-A</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E281" t="n">
         <v>28</v>
@@ -12962,21 +12944,21 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>R2-09-D</t>
+          <t>R3-09-A</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E282" t="n">
         <v>29</v>
@@ -12988,21 +12970,21 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>R2-10-D</t>
+          <t>R3-10-A</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E283" t="n">
         <v>30</v>
@@ -13014,21 +12996,21 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>R2-11-D</t>
+          <t>R3-11-A</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E284" t="n">
         <v>31</v>
@@ -13040,21 +13022,21 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>R2-12-D</t>
+          <t>R3-12-A</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E285" t="n">
         <v>32</v>
@@ -13066,21 +13048,21 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>R2-13-D</t>
+          <t>R3-13-A</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E286" t="n">
         <v>33</v>
@@ -13092,21 +13074,21 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>R2-14-D</t>
+          <t>R3-14-A</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E287" t="n">
         <v>34</v>
@@ -13118,21 +13100,21 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>R2-15-D</t>
+          <t>R3-15-A</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E288" t="n">
         <v>35</v>
@@ -13144,21 +13126,21 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>R2-16-D</t>
+          <t>R3-16-A</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E289" t="n">
         <v>36</v>
@@ -13170,7 +13152,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>R3-01-A</t>
+          <t>R3-01-B</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13184,7 +13166,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E290" t="n">
         <v>21</v>
@@ -13196,7 +13178,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>R3-02-A</t>
+          <t>R3-02-B</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13210,7 +13192,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E291" t="n">
         <v>22</v>
@@ -13222,7 +13204,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>R3-03-A</t>
+          <t>R3-03-B</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13236,7 +13218,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E292" t="n">
         <v>23</v>
@@ -13248,7 +13230,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>R3-04-A</t>
+          <t>R3-04-B</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13262,7 +13244,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E293" t="n">
         <v>24</v>
@@ -13274,7 +13256,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>R3-05-A</t>
+          <t>R3-05-B</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13288,7 +13270,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E294" t="n">
         <v>25</v>
@@ -13300,7 +13282,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>R3-06-A</t>
+          <t>R3-06-B</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13314,7 +13296,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E295" t="n">
         <v>26</v>
@@ -13326,7 +13308,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>R3-07-A</t>
+          <t>R3-07-B</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13340,7 +13322,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E296" t="n">
         <v>27</v>
@@ -13352,7 +13334,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>R3-08-A</t>
+          <t>R3-08-B</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13366,7 +13348,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E297" t="n">
         <v>28</v>
@@ -13378,7 +13360,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>R3-09-A</t>
+          <t>R3-09-B</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13392,7 +13374,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E298" t="n">
         <v>29</v>
@@ -13404,7 +13386,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>R3-10-A</t>
+          <t>R3-10-B</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13418,7 +13400,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E299" t="n">
         <v>30</v>
@@ -13430,7 +13412,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>R3-11-A</t>
+          <t>R3-11-B</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13444,7 +13426,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E300" t="n">
         <v>31</v>
@@ -13456,7 +13438,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>R3-12-A</t>
+          <t>R3-12-B</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13470,7 +13452,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E301" t="n">
         <v>32</v>
@@ -13482,7 +13464,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>R3-13-A</t>
+          <t>R3-13-B</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13496,7 +13478,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E302" t="n">
         <v>33</v>
@@ -13508,7 +13490,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>R3-14-A</t>
+          <t>R3-14-B</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13522,7 +13504,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E303" t="n">
         <v>34</v>
@@ -13534,7 +13516,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>R3-15-A</t>
+          <t>R3-15-B</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13548,7 +13530,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E304" t="n">
         <v>35</v>
@@ -13560,7 +13542,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>R3-16-A</t>
+          <t>R3-16-B</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13574,7 +13556,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E305" t="n">
         <v>36</v>
@@ -13586,7 +13568,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>R3-01-B</t>
+          <t>R3-01-C</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13600,7 +13582,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E306" t="n">
         <v>21</v>
@@ -13612,7 +13594,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>R3-02-B</t>
+          <t>R3-02-C</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13626,7 +13608,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E307" t="n">
         <v>22</v>
@@ -13638,7 +13620,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>R3-03-B</t>
+          <t>R3-03-C</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13652,7 +13634,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E308" t="n">
         <v>23</v>
@@ -13664,7 +13646,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>R3-04-B</t>
+          <t>R3-04-C</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13678,7 +13660,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E309" t="n">
         <v>24</v>
@@ -13690,7 +13672,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>R3-05-B</t>
+          <t>R3-05-C</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13704,7 +13686,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E310" t="n">
         <v>25</v>
@@ -13716,7 +13698,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>R3-06-B</t>
+          <t>R3-06-C</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13730,7 +13712,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E311" t="n">
         <v>26</v>
@@ -13742,7 +13724,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>R3-07-B</t>
+          <t>R3-07-C</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13756,7 +13738,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E312" t="n">
         <v>27</v>
@@ -13768,7 +13750,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>R3-08-B</t>
+          <t>R3-08-C</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13782,7 +13764,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E313" t="n">
         <v>28</v>
@@ -13794,7 +13776,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>R3-09-B</t>
+          <t>R3-09-C</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13808,7 +13790,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E314" t="n">
         <v>29</v>
@@ -13820,7 +13802,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>R3-10-B</t>
+          <t>R3-10-C</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13834,7 +13816,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E315" t="n">
         <v>30</v>
@@ -13846,7 +13828,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>R3-11-B</t>
+          <t>R3-11-C</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -13860,7 +13842,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E316" t="n">
         <v>31</v>
@@ -13872,7 +13854,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>R3-12-B</t>
+          <t>R3-12-C</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -13886,7 +13868,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E317" t="n">
         <v>32</v>
@@ -13898,7 +13880,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>R3-13-B</t>
+          <t>R3-13-C</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -13912,7 +13894,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E318" t="n">
         <v>33</v>
@@ -13924,7 +13906,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>R3-14-B</t>
+          <t>R3-14-C</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -13938,7 +13920,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E319" t="n">
         <v>34</v>
@@ -13950,7 +13932,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>R3-15-B</t>
+          <t>R3-15-C</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -13964,7 +13946,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E320" t="n">
         <v>35</v>
@@ -13976,7 +13958,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>R3-16-B</t>
+          <t>R3-16-C</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -13990,7 +13972,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E321" t="n">
         <v>36</v>
@@ -14002,7 +13984,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>R3-01-C</t>
+          <t>R3-01-D</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14016,7 +13998,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E322" t="n">
         <v>21</v>
@@ -14028,7 +14010,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>R3-02-C</t>
+          <t>R3-02-D</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14042,7 +14024,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E323" t="n">
         <v>22</v>
@@ -14054,7 +14036,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>R3-03-C</t>
+          <t>R3-03-D</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14068,7 +14050,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E324" t="n">
         <v>23</v>
@@ -14080,7 +14062,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>R3-04-C</t>
+          <t>R3-04-D</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14094,7 +14076,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E325" t="n">
         <v>24</v>
@@ -14106,7 +14088,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>R3-05-C</t>
+          <t>R3-05-D</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14120,7 +14102,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E326" t="n">
         <v>25</v>
@@ -14132,7 +14114,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>R3-06-C</t>
+          <t>R3-06-D</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14146,7 +14128,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E327" t="n">
         <v>26</v>
@@ -14158,7 +14140,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>R3-07-C</t>
+          <t>R3-07-D</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14172,7 +14154,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E328" t="n">
         <v>27</v>
@@ -14184,7 +14166,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>R3-08-C</t>
+          <t>R3-08-D</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14198,7 +14180,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E329" t="n">
         <v>28</v>
@@ -14210,7 +14192,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>R3-09-C</t>
+          <t>R3-09-D</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14224,7 +14206,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E330" t="n">
         <v>29</v>
@@ -14236,7 +14218,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>R3-10-C</t>
+          <t>R3-10-D</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14250,7 +14232,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E331" t="n">
         <v>30</v>
@@ -14262,7 +14244,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>R3-11-C</t>
+          <t>R3-11-D</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14276,7 +14258,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E332" t="n">
         <v>31</v>
@@ -14288,7 +14270,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>R3-12-C</t>
+          <t>R3-12-D</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14302,7 +14284,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E333" t="n">
         <v>32</v>
@@ -14314,7 +14296,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>R3-13-C</t>
+          <t>R3-13-D</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14328,7 +14310,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E334" t="n">
         <v>33</v>
@@ -14340,7 +14322,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>R3-14-C</t>
+          <t>R3-14-D</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14354,7 +14336,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E335" t="n">
         <v>34</v>
@@ -14366,7 +14348,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>R3-15-C</t>
+          <t>R3-15-D</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14380,7 +14362,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E336" t="n">
         <v>35</v>
@@ -14392,7 +14374,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>R3-16-C</t>
+          <t>R3-16-D</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14406,7 +14388,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E337" t="n">
         <v>36</v>
@@ -14418,21 +14400,21 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>R3-01-D</t>
+          <t>R4-01-A</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E338" t="n">
         <v>21</v>
@@ -14444,21 +14426,21 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>R3-02-D</t>
+          <t>R4-02-A</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E339" t="n">
         <v>22</v>
@@ -14470,21 +14452,21 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>R3-03-D</t>
+          <t>R4-03-A</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E340" t="n">
         <v>23</v>
@@ -14496,21 +14478,21 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>R3-04-D</t>
+          <t>R4-04-A</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E341" t="n">
         <v>24</v>
@@ -14522,21 +14504,21 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>R3-05-D</t>
+          <t>R4-05-A</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E342" t="n">
         <v>25</v>
@@ -14548,21 +14530,21 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>R3-06-D</t>
+          <t>R4-06-A</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E343" t="n">
         <v>26</v>
@@ -14574,21 +14556,21 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>R3-07-D</t>
+          <t>R4-07-A</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E344" t="n">
         <v>27</v>
@@ -14600,21 +14582,21 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>R3-08-D</t>
+          <t>R4-08-A</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E345" t="n">
         <v>28</v>
@@ -14626,21 +14608,21 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>R3-09-D</t>
+          <t>R4-09-A</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E346" t="n">
         <v>29</v>
@@ -14652,21 +14634,21 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>R3-10-D</t>
+          <t>R4-10-A</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E347" t="n">
         <v>30</v>
@@ -14678,21 +14660,21 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>R3-11-D</t>
+          <t>R4-11-A</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E348" t="n">
         <v>31</v>
@@ -14704,21 +14686,21 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>R3-12-D</t>
+          <t>R4-12-A</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E349" t="n">
         <v>32</v>
@@ -14730,21 +14712,21 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>R3-13-D</t>
+          <t>R4-13-A</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E350" t="n">
         <v>33</v>
@@ -14756,21 +14738,21 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>R3-14-D</t>
+          <t>R4-14-A</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E351" t="n">
         <v>34</v>
@@ -14782,21 +14764,21 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>R3-15-D</t>
+          <t>R4-15-A</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E352" t="n">
         <v>35</v>
@@ -14808,21 +14790,21 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>R3-16-D</t>
+          <t>R4-16-A</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E353" t="n">
         <v>36</v>
@@ -14834,7 +14816,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>R4-01-A</t>
+          <t>R4-01-B</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14848,7 +14830,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E354" t="n">
         <v>21</v>
@@ -14860,7 +14842,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>R4-02-A</t>
+          <t>R4-02-B</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14874,7 +14856,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E355" t="n">
         <v>22</v>
@@ -14886,7 +14868,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>R4-03-A</t>
+          <t>R4-03-B</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14900,7 +14882,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E356" t="n">
         <v>23</v>
@@ -14912,7 +14894,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>R4-04-A</t>
+          <t>R4-04-B</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14926,7 +14908,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E357" t="n">
         <v>24</v>
@@ -14938,7 +14920,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>R4-05-A</t>
+          <t>R4-05-B</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14952,7 +14934,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E358" t="n">
         <v>25</v>
@@ -14964,7 +14946,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>R4-06-A</t>
+          <t>R4-06-B</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14978,7 +14960,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E359" t="n">
         <v>26</v>
@@ -14990,7 +14972,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>R4-07-A</t>
+          <t>R4-07-B</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -15004,7 +14986,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E360" t="n">
         <v>27</v>
@@ -15016,7 +14998,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>R4-08-A</t>
+          <t>R4-08-B</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -15030,7 +15012,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E361" t="n">
         <v>28</v>
@@ -15042,7 +15024,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>R4-09-A</t>
+          <t>R4-09-B</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -15056,7 +15038,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E362" t="n">
         <v>29</v>
@@ -15068,7 +15050,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>R4-10-A</t>
+          <t>R4-10-B</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -15082,7 +15064,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E363" t="n">
         <v>30</v>
@@ -15094,7 +15076,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>R4-11-A</t>
+          <t>R4-11-B</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -15108,7 +15090,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E364" t="n">
         <v>31</v>
@@ -15120,7 +15102,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>R4-12-A</t>
+          <t>R4-12-B</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -15134,7 +15116,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E365" t="n">
         <v>32</v>
@@ -15146,7 +15128,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>R4-13-A</t>
+          <t>R4-13-B</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -15160,7 +15142,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E366" t="n">
         <v>33</v>
@@ -15172,7 +15154,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>R4-14-A</t>
+          <t>R4-14-B</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15186,7 +15168,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E367" t="n">
         <v>34</v>
@@ -15198,7 +15180,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>R4-15-A</t>
+          <t>R4-15-B</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -15212,7 +15194,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E368" t="n">
         <v>35</v>
@@ -15224,7 +15206,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>R4-16-A</t>
+          <t>R4-16-B</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15238,7 +15220,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E369" t="n">
         <v>36</v>
@@ -15250,7 +15232,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>R4-01-B</t>
+          <t>R4-01-C</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15264,7 +15246,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E370" t="n">
         <v>21</v>
@@ -15276,7 +15258,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>R4-02-B</t>
+          <t>R4-02-C</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -15290,7 +15272,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E371" t="n">
         <v>22</v>
@@ -15302,7 +15284,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>R4-03-B</t>
+          <t>R4-03-C</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15316,7 +15298,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E372" t="n">
         <v>23</v>
@@ -15328,7 +15310,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>R4-04-B</t>
+          <t>R4-04-C</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15342,7 +15324,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E373" t="n">
         <v>24</v>
@@ -15354,7 +15336,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>R4-05-B</t>
+          <t>R4-05-C</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15368,7 +15350,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E374" t="n">
         <v>25</v>
@@ -15380,7 +15362,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>R4-06-B</t>
+          <t>R4-06-C</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15394,7 +15376,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E375" t="n">
         <v>26</v>
@@ -15406,7 +15388,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>R4-07-B</t>
+          <t>R4-07-C</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15420,7 +15402,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E376" t="n">
         <v>27</v>
@@ -15432,7 +15414,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>R4-08-B</t>
+          <t>R4-08-C</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15446,7 +15428,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E377" t="n">
         <v>28</v>
@@ -15458,7 +15440,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>R4-09-B</t>
+          <t>R4-09-C</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15472,7 +15454,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E378" t="n">
         <v>29</v>
@@ -15484,7 +15466,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>R4-10-B</t>
+          <t>R4-10-C</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15498,7 +15480,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E379" t="n">
         <v>30</v>
@@ -15510,7 +15492,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>R4-11-B</t>
+          <t>R4-11-C</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15524,7 +15506,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E380" t="n">
         <v>31</v>
@@ -15536,7 +15518,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>R4-12-B</t>
+          <t>R4-12-C</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15550,7 +15532,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E381" t="n">
         <v>32</v>
@@ -15562,7 +15544,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>R4-13-B</t>
+          <t>R4-13-C</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15576,7 +15558,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E382" t="n">
         <v>33</v>
@@ -15588,7 +15570,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>R4-14-B</t>
+          <t>R4-14-C</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15602,7 +15584,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E383" t="n">
         <v>34</v>
@@ -15614,7 +15596,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>R4-15-B</t>
+          <t>R4-15-C</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15628,7 +15610,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E384" t="n">
         <v>35</v>
@@ -15640,7 +15622,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>R4-16-B</t>
+          <t>R4-16-C</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15654,7 +15636,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E385" t="n">
         <v>36</v>
@@ -15666,7 +15648,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>R4-01-C</t>
+          <t>R4-01-D</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15680,7 +15662,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E386" t="n">
         <v>21</v>
@@ -15692,7 +15674,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>R4-02-C</t>
+          <t>R4-02-D</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15706,7 +15688,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E387" t="n">
         <v>22</v>
@@ -15718,7 +15700,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>R4-03-C</t>
+          <t>R4-03-D</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15732,7 +15714,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E388" t="n">
         <v>23</v>
@@ -15744,7 +15726,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>R4-04-C</t>
+          <t>R4-04-D</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15758,7 +15740,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E389" t="n">
         <v>24</v>
@@ -15770,7 +15752,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>R4-05-C</t>
+          <t>R4-05-D</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15784,7 +15766,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E390" t="n">
         <v>25</v>
@@ -15796,7 +15778,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>R4-06-C</t>
+          <t>R4-06-D</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15810,7 +15792,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E391" t="n">
         <v>26</v>
@@ -15822,7 +15804,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>R4-07-C</t>
+          <t>R4-07-D</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15836,7 +15818,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E392" t="n">
         <v>27</v>
@@ -15848,7 +15830,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>R4-08-C</t>
+          <t>R4-08-D</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15862,7 +15844,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E393" t="n">
         <v>28</v>
@@ -15874,7 +15856,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>R4-09-C</t>
+          <t>R4-09-D</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15888,7 +15870,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E394" t="n">
         <v>29</v>
@@ -15900,7 +15882,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>R4-10-C</t>
+          <t>R4-10-D</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15914,7 +15896,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E395" t="n">
         <v>30</v>
@@ -15926,7 +15908,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>R4-11-C</t>
+          <t>R4-11-D</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15940,7 +15922,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E396" t="n">
         <v>31</v>
@@ -15952,7 +15934,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>R4-12-C</t>
+          <t>R4-12-D</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15966,7 +15948,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E397" t="n">
         <v>32</v>
@@ -15978,7 +15960,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>R4-13-C</t>
+          <t>R4-13-D</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15992,7 +15974,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E398" t="n">
         <v>33</v>
@@ -16004,7 +15986,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>R4-14-C</t>
+          <t>R4-14-D</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -16018,7 +16000,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E399" t="n">
         <v>34</v>
@@ -16030,7 +16012,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>R4-15-C</t>
+          <t>R4-15-D</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -16044,7 +16026,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E400" t="n">
         <v>35</v>
@@ -16056,7 +16038,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>R4-16-C</t>
+          <t>R4-16-D</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -16070,428 +16052,12 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E401" t="n">
         <v>36</v>
       </c>
       <c r="F401" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>R4-01-D</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D402" t="n">
-        <v>10</v>
-      </c>
-      <c r="E402" t="n">
-        <v>21</v>
-      </c>
-      <c r="F402" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>R4-02-D</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D403" t="n">
-        <v>10</v>
-      </c>
-      <c r="E403" t="n">
-        <v>22</v>
-      </c>
-      <c r="F403" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>R4-03-D</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D404" t="n">
-        <v>10</v>
-      </c>
-      <c r="E404" t="n">
-        <v>23</v>
-      </c>
-      <c r="F404" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>R4-04-D</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D405" t="n">
-        <v>10</v>
-      </c>
-      <c r="E405" t="n">
-        <v>24</v>
-      </c>
-      <c r="F405" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>R4-05-D</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D406" t="n">
-        <v>10</v>
-      </c>
-      <c r="E406" t="n">
-        <v>25</v>
-      </c>
-      <c r="F406" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>R4-06-D</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D407" t="n">
-        <v>10</v>
-      </c>
-      <c r="E407" t="n">
-        <v>26</v>
-      </c>
-      <c r="F407" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>R4-07-D</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D408" t="n">
-        <v>10</v>
-      </c>
-      <c r="E408" t="n">
-        <v>27</v>
-      </c>
-      <c r="F408" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>R4-08-D</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D409" t="n">
-        <v>10</v>
-      </c>
-      <c r="E409" t="n">
-        <v>28</v>
-      </c>
-      <c r="F409" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>R4-09-D</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D410" t="n">
-        <v>10</v>
-      </c>
-      <c r="E410" t="n">
-        <v>29</v>
-      </c>
-      <c r="F410" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>R4-10-D</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D411" t="n">
-        <v>10</v>
-      </c>
-      <c r="E411" t="n">
-        <v>30</v>
-      </c>
-      <c r="F411" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>R4-11-D</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D412" t="n">
-        <v>10</v>
-      </c>
-      <c r="E412" t="n">
-        <v>31</v>
-      </c>
-      <c r="F412" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>R4-12-D</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D413" t="n">
-        <v>10</v>
-      </c>
-      <c r="E413" t="n">
-        <v>32</v>
-      </c>
-      <c r="F413" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>R4-13-D</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D414" t="n">
-        <v>10</v>
-      </c>
-      <c r="E414" t="n">
-        <v>33</v>
-      </c>
-      <c r="F414" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>R4-14-D</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D415" t="n">
-        <v>10</v>
-      </c>
-      <c r="E415" t="n">
-        <v>34</v>
-      </c>
-      <c r="F415" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>R4-15-D</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D416" t="n">
-        <v>10</v>
-      </c>
-      <c r="E416" t="n">
-        <v>35</v>
-      </c>
-      <c r="F416" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>R4-16-D</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="D417" t="n">
-        <v>10</v>
-      </c>
-      <c r="E417" t="n">
-        <v>36</v>
-      </c>
-      <c r="F417" t="n">
         <v>16</v>
       </c>
     </row>

--- a/Floor_Map_Simple.xlsx
+++ b/Floor_Map_Simple.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Map" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stock" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Moves" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="Squares" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Layout" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Moves" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lists" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Squares" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="zn_BOX">Stock!$I$5</definedName>
@@ -254,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -345,6 +346,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -513,11 +515,27 @@
     <tableColumn id="3" name="Zone"/>
     <tableColumn id="4" name="Low when pallets at or below"/>
     <tableColumn id="5" name="Pallets on map">
-      <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$27,tblStock[[#This Row],[Item code]]))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$DZ$300,tblStock[[#This Row],[Item code]]))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" name="Status">
       <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblLayout" displayName="tblLayout" ref="A5:G14" headerRowCount="1">
+  <autoFilter ref="A5:G14"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Aisle"/>
+    <tableColumn id="2" name="Side"/>
+    <tableColumn id="3" name="Order from fire exit"/>
+    <tableColumn id="4" name="Rows"/>
+    <tableColumn id="5" name="Pallets deep"/>
+    <tableColumn id="6" name="Zone"/>
+    <tableColumn id="7" name="Use"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showRowStripes="1"/>
 </table>
@@ -2026,7 +2044,7 @@
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31">
-        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$27,tblStock[[#This Row],[Item code]]))</f>
+        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$DZ$300,tblStock[[#This Row],[Item code]]))</f>
         <v/>
       </c>
       <c r="F5" s="29">
@@ -2073,7 +2091,7 @@
       </c>
       <c r="D6" s="31" t="n"/>
       <c r="E6" s="31">
-        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$AJ$27,tblStock[[#This Row],[Item code]]))</f>
+        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$DZ$300,tblStock[[#This Row],[Item code]]))</f>
         <v/>
       </c>
       <c r="F6" s="29">
@@ -2187,6 +2205,422 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="38" t="inlineStr">
+        <is>
+          <t>Change the numbers, then press the REBUILD MAP button. Pallets already on the map stay where they are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Aisle</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Order from fire exit</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>Pallets deep</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="31" t="inlineStr"/>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>XR</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="31" t="inlineStr"/>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>LBL</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>FLM</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>Rows = how many pallets wide the aisle is (1 row = 1 line of pallets on the map).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>Pallets deep = how many pallets from the walkway to the wall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>Side: Left or Right, standing with the fire exit behind you. Order: 1 = nearest the fire exit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>Use: Yes = ours,  Blocked = someone else's (grey),  No = hide it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>Zone codes: BOX = Boxes,  BAG = Bags,  FLM = Films and Wrap,  LBL = Labels and Packing   (rename zones on the Stock sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>New aisle? Type it on the first empty row under the table.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="B6:B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Left,Right"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G6:G60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Blocked,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"BOX,BAG,FLM,LBL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C6:E60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Use a whole number from 1 to 60." type="whole" operator="between">
+      <formula1>1</formula1>
+      <formula2>60</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2211,39 +2645,39 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Filled in automatically by the macros. Newest at the bottom.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>When</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="40" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>To</t>
         </is>
@@ -2257,7 +2691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5620,7 +6054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Floor_Map_Simple.xlsx
+++ b/Floor_Map_Simple.xlsx
@@ -508,17 +508,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblStock" displayName="tblStock" ref="A4:F6" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblStock" displayName="tblStock" ref="A4:F154" headerRowCount="1">
   <tableColumns count="6">
     <tableColumn id="1" name="Item code"/>
     <tableColumn id="2" name="Description"/>
     <tableColumn id="3" name="Zone"/>
     <tableColumn id="4" name="Low when pallets at or below"/>
     <tableColumn id="5" name="Pallets on map">
-      <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$DZ$300,tblStock[[#This Row],[Item code]]))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" name="Status">
-      <calculatedColumnFormula>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showRowStripes="1"/>
@@ -1934,7 +1934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2044,11 +2044,11 @@
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31">
-        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$DZ$300,tblStock[[#This Row],[Item code]]))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F5" s="29">
-        <f>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
         <v/>
       </c>
       <c r="H5" s="32" t="inlineStr">
@@ -2091,11 +2091,11 @@
       </c>
       <c r="D6" s="31" t="n"/>
       <c r="E6" s="31">
-        <f>IF(tblStock[[#This Row],[Item code]]="","",COUNTIF(Map!$A$6:$DZ$300,tblStock[[#This Row],[Item code]]))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F6" s="29">
-        <f>IF(tblStock[[#This Row],[Item code]]="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
         <v/>
       </c>
       <c r="H6" s="34" t="inlineStr">
@@ -2121,6 +2121,18 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="29" t="n"/>
+      <c r="B7" s="30" t="n"/>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F7" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
           <t>FLM</t>
@@ -2144,6 +2156,18 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="30" t="n"/>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F8" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
       <c r="H8" s="36" t="inlineStr">
         <is>
           <t>LBL</t>
@@ -2166,11 +2190,2053 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="30" t="n"/>
+      <c r="C9" s="31" t="n"/>
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F9" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
       <c r="H9" s="37" t="inlineStr">
         <is>
           <t>Type over a zone name (pink box) and the Map changes too. In the Zone column on the left, use the Code.</t>
         </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="29" t="n"/>
+      <c r="B10" s="30" t="n"/>
+      <c r="C10" s="31" t="n"/>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F10" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="29" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F11" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="29" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="29" t="n"/>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F14" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F15" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="30" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F16" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="29" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="30" t="n"/>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F21" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="30" t="n"/>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="30" t="n"/>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F24" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="29" t="n"/>
+      <c r="B25" s="30" t="n"/>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F25" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F26" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F27" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="29" t="n"/>
+      <c r="B28" s="30" t="n"/>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F28" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="29" t="n"/>
+      <c r="B29" s="30" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F29" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="30" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F30" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="30" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F31" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="29" t="n"/>
+      <c r="B32" s="30" t="n"/>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F32" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F33" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="29" t="n"/>
+      <c r="B34" s="30" t="n"/>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F34" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="29" t="n"/>
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F35" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="29" t="n"/>
+      <c r="B36" s="30" t="n"/>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F36" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="29" t="n"/>
+      <c r="B37" s="30" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F37" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="29" t="n"/>
+      <c r="B38" s="30" t="n"/>
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F38" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F39" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="30" t="n"/>
+      <c r="C40" s="31" t="n"/>
+      <c r="D40" s="31" t="n"/>
+      <c r="E40" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F40" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="29" t="n"/>
+      <c r="B41" s="30" t="n"/>
+      <c r="C41" s="31" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F41" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="30" t="n"/>
+      <c r="C42" s="31" t="n"/>
+      <c r="D42" s="31" t="n"/>
+      <c r="E42" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F42" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="29" t="n"/>
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="31" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F43" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="29" t="n"/>
+      <c r="B44" s="30" t="n"/>
+      <c r="C44" s="31" t="n"/>
+      <c r="D44" s="31" t="n"/>
+      <c r="E44" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F44" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="29" t="n"/>
+      <c r="B45" s="30" t="n"/>
+      <c r="C45" s="31" t="n"/>
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F45" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="29" t="n"/>
+      <c r="B46" s="30" t="n"/>
+      <c r="C46" s="31" t="n"/>
+      <c r="D46" s="31" t="n"/>
+      <c r="E46" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F46" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="29" t="n"/>
+      <c r="B47" s="30" t="n"/>
+      <c r="C47" s="31" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="E47" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F47" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="29" t="n"/>
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="31" t="n"/>
+      <c r="D48" s="31" t="n"/>
+      <c r="E48" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F48" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="29" t="n"/>
+      <c r="B49" s="30" t="n"/>
+      <c r="C49" s="31" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F49" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="29" t="n"/>
+      <c r="B50" s="30" t="n"/>
+      <c r="C50" s="31" t="n"/>
+      <c r="D50" s="31" t="n"/>
+      <c r="E50" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F50" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="29" t="n"/>
+      <c r="B51" s="30" t="n"/>
+      <c r="C51" s="31" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F51" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="29" t="n"/>
+      <c r="B52" s="30" t="n"/>
+      <c r="C52" s="31" t="n"/>
+      <c r="D52" s="31" t="n"/>
+      <c r="E52" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F52" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="29" t="n"/>
+      <c r="B53" s="30" t="n"/>
+      <c r="C53" s="31" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F53" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="29" t="n"/>
+      <c r="B54" s="30" t="n"/>
+      <c r="C54" s="31" t="n"/>
+      <c r="D54" s="31" t="n"/>
+      <c r="E54" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F54" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="29" t="n"/>
+      <c r="B55" s="30" t="n"/>
+      <c r="C55" s="31" t="n"/>
+      <c r="D55" s="31" t="n"/>
+      <c r="E55" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F55" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="29" t="n"/>
+      <c r="B56" s="30" t="n"/>
+      <c r="C56" s="31" t="n"/>
+      <c r="D56" s="31" t="n"/>
+      <c r="E56" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F56" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="29" t="n"/>
+      <c r="B57" s="30" t="n"/>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F57" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="29" t="n"/>
+      <c r="B58" s="30" t="n"/>
+      <c r="C58" s="31" t="n"/>
+      <c r="D58" s="31" t="n"/>
+      <c r="E58" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F58" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="29" t="n"/>
+      <c r="B59" s="30" t="n"/>
+      <c r="C59" s="31" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F59" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="29" t="n"/>
+      <c r="B60" s="30" t="n"/>
+      <c r="C60" s="31" t="n"/>
+      <c r="D60" s="31" t="n"/>
+      <c r="E60" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F60" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="29" t="n"/>
+      <c r="B61" s="30" t="n"/>
+      <c r="C61" s="31" t="n"/>
+      <c r="D61" s="31" t="n"/>
+      <c r="E61" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F61" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="29" t="n"/>
+      <c r="B62" s="30" t="n"/>
+      <c r="C62" s="31" t="n"/>
+      <c r="D62" s="31" t="n"/>
+      <c r="E62" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F62" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="29" t="n"/>
+      <c r="B63" s="30" t="n"/>
+      <c r="C63" s="31" t="n"/>
+      <c r="D63" s="31" t="n"/>
+      <c r="E63" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F63" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="29" t="n"/>
+      <c r="B64" s="30" t="n"/>
+      <c r="C64" s="31" t="n"/>
+      <c r="D64" s="31" t="n"/>
+      <c r="E64" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F64" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="29" t="n"/>
+      <c r="B65" s="30" t="n"/>
+      <c r="C65" s="31" t="n"/>
+      <c r="D65" s="31" t="n"/>
+      <c r="E65" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F65" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="29" t="n"/>
+      <c r="B66" s="30" t="n"/>
+      <c r="C66" s="31" t="n"/>
+      <c r="D66" s="31" t="n"/>
+      <c r="E66" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F66" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="29" t="n"/>
+      <c r="B67" s="30" t="n"/>
+      <c r="C67" s="31" t="n"/>
+      <c r="D67" s="31" t="n"/>
+      <c r="E67" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F67" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="29" t="n"/>
+      <c r="B68" s="30" t="n"/>
+      <c r="C68" s="31" t="n"/>
+      <c r="D68" s="31" t="n"/>
+      <c r="E68" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F68" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="29" t="n"/>
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="31" t="n"/>
+      <c r="D69" s="31" t="n"/>
+      <c r="E69" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F69" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="29" t="n"/>
+      <c r="B70" s="30" t="n"/>
+      <c r="C70" s="31" t="n"/>
+      <c r="D70" s="31" t="n"/>
+      <c r="E70" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F70" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="29" t="n"/>
+      <c r="B71" s="30" t="n"/>
+      <c r="C71" s="31" t="n"/>
+      <c r="D71" s="31" t="n"/>
+      <c r="E71" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F71" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="29" t="n"/>
+      <c r="B72" s="30" t="n"/>
+      <c r="C72" s="31" t="n"/>
+      <c r="D72" s="31" t="n"/>
+      <c r="E72" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F72" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="29" t="n"/>
+      <c r="B73" s="30" t="n"/>
+      <c r="C73" s="31" t="n"/>
+      <c r="D73" s="31" t="n"/>
+      <c r="E73" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F73" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="29" t="n"/>
+      <c r="B74" s="30" t="n"/>
+      <c r="C74" s="31" t="n"/>
+      <c r="D74" s="31" t="n"/>
+      <c r="E74" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F74" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="29" t="n"/>
+      <c r="B75" s="30" t="n"/>
+      <c r="C75" s="31" t="n"/>
+      <c r="D75" s="31" t="n"/>
+      <c r="E75" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F75" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="29" t="n"/>
+      <c r="B76" s="30" t="n"/>
+      <c r="C76" s="31" t="n"/>
+      <c r="D76" s="31" t="n"/>
+      <c r="E76" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F76" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="29" t="n"/>
+      <c r="B77" s="30" t="n"/>
+      <c r="C77" s="31" t="n"/>
+      <c r="D77" s="31" t="n"/>
+      <c r="E77" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F77" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="29" t="n"/>
+      <c r="B78" s="30" t="n"/>
+      <c r="C78" s="31" t="n"/>
+      <c r="D78" s="31" t="n"/>
+      <c r="E78" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F78" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="29" t="n"/>
+      <c r="B79" s="30" t="n"/>
+      <c r="C79" s="31" t="n"/>
+      <c r="D79" s="31" t="n"/>
+      <c r="E79" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F79" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="29" t="n"/>
+      <c r="B80" s="30" t="n"/>
+      <c r="C80" s="31" t="n"/>
+      <c r="D80" s="31" t="n"/>
+      <c r="E80" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F80" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="29" t="n"/>
+      <c r="B81" s="30" t="n"/>
+      <c r="C81" s="31" t="n"/>
+      <c r="D81" s="31" t="n"/>
+      <c r="E81" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F81" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="29" t="n"/>
+      <c r="B82" s="30" t="n"/>
+      <c r="C82" s="31" t="n"/>
+      <c r="D82" s="31" t="n"/>
+      <c r="E82" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F82" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="29" t="n"/>
+      <c r="B83" s="30" t="n"/>
+      <c r="C83" s="31" t="n"/>
+      <c r="D83" s="31" t="n"/>
+      <c r="E83" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F83" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="29" t="n"/>
+      <c r="B84" s="30" t="n"/>
+      <c r="C84" s="31" t="n"/>
+      <c r="D84" s="31" t="n"/>
+      <c r="E84" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F84" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="29" t="n"/>
+      <c r="B85" s="30" t="n"/>
+      <c r="C85" s="31" t="n"/>
+      <c r="D85" s="31" t="n"/>
+      <c r="E85" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F85" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="29" t="n"/>
+      <c r="B86" s="30" t="n"/>
+      <c r="C86" s="31" t="n"/>
+      <c r="D86" s="31" t="n"/>
+      <c r="E86" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F86" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="29" t="n"/>
+      <c r="B87" s="30" t="n"/>
+      <c r="C87" s="31" t="n"/>
+      <c r="D87" s="31" t="n"/>
+      <c r="E87" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F87" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="29" t="n"/>
+      <c r="B88" s="30" t="n"/>
+      <c r="C88" s="31" t="n"/>
+      <c r="D88" s="31" t="n"/>
+      <c r="E88" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F88" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="29" t="n"/>
+      <c r="B89" s="30" t="n"/>
+      <c r="C89" s="31" t="n"/>
+      <c r="D89" s="31" t="n"/>
+      <c r="E89" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F89" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="29" t="n"/>
+      <c r="B90" s="30" t="n"/>
+      <c r="C90" s="31" t="n"/>
+      <c r="D90" s="31" t="n"/>
+      <c r="E90" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F90" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="29" t="n"/>
+      <c r="B91" s="30" t="n"/>
+      <c r="C91" s="31" t="n"/>
+      <c r="D91" s="31" t="n"/>
+      <c r="E91" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F91" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="29" t="n"/>
+      <c r="B92" s="30" t="n"/>
+      <c r="C92" s="31" t="n"/>
+      <c r="D92" s="31" t="n"/>
+      <c r="E92" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F92" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="29" t="n"/>
+      <c r="B93" s="30" t="n"/>
+      <c r="C93" s="31" t="n"/>
+      <c r="D93" s="31" t="n"/>
+      <c r="E93" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F93" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="29" t="n"/>
+      <c r="B94" s="30" t="n"/>
+      <c r="C94" s="31" t="n"/>
+      <c r="D94" s="31" t="n"/>
+      <c r="E94" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F94" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="29" t="n"/>
+      <c r="B95" s="30" t="n"/>
+      <c r="C95" s="31" t="n"/>
+      <c r="D95" s="31" t="n"/>
+      <c r="E95" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F95" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="29" t="n"/>
+      <c r="B96" s="30" t="n"/>
+      <c r="C96" s="31" t="n"/>
+      <c r="D96" s="31" t="n"/>
+      <c r="E96" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F96" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="29" t="n"/>
+      <c r="B97" s="30" t="n"/>
+      <c r="C97" s="31" t="n"/>
+      <c r="D97" s="31" t="n"/>
+      <c r="E97" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F97" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="29" t="n"/>
+      <c r="B98" s="30" t="n"/>
+      <c r="C98" s="31" t="n"/>
+      <c r="D98" s="31" t="n"/>
+      <c r="E98" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F98" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="29" t="n"/>
+      <c r="B99" s="30" t="n"/>
+      <c r="C99" s="31" t="n"/>
+      <c r="D99" s="31" t="n"/>
+      <c r="E99" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F99" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="29" t="n"/>
+      <c r="B100" s="30" t="n"/>
+      <c r="C100" s="31" t="n"/>
+      <c r="D100" s="31" t="n"/>
+      <c r="E100" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F100" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="29" t="n"/>
+      <c r="B101" s="30" t="n"/>
+      <c r="C101" s="31" t="n"/>
+      <c r="D101" s="31" t="n"/>
+      <c r="E101" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F101" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="29" t="n"/>
+      <c r="B102" s="30" t="n"/>
+      <c r="C102" s="31" t="n"/>
+      <c r="D102" s="31" t="n"/>
+      <c r="E102" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F102" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="29" t="n"/>
+      <c r="B103" s="30" t="n"/>
+      <c r="C103" s="31" t="n"/>
+      <c r="D103" s="31" t="n"/>
+      <c r="E103" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F103" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="29" t="n"/>
+      <c r="B104" s="30" t="n"/>
+      <c r="C104" s="31" t="n"/>
+      <c r="D104" s="31" t="n"/>
+      <c r="E104" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F104" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="29" t="n"/>
+      <c r="B105" s="30" t="n"/>
+      <c r="C105" s="31" t="n"/>
+      <c r="D105" s="31" t="n"/>
+      <c r="E105" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F105" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="29" t="n"/>
+      <c r="B106" s="30" t="n"/>
+      <c r="C106" s="31" t="n"/>
+      <c r="D106" s="31" t="n"/>
+      <c r="E106" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F106" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="29" t="n"/>
+      <c r="B107" s="30" t="n"/>
+      <c r="C107" s="31" t="n"/>
+      <c r="D107" s="31" t="n"/>
+      <c r="E107" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F107" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="29" t="n"/>
+      <c r="B108" s="30" t="n"/>
+      <c r="C108" s="31" t="n"/>
+      <c r="D108" s="31" t="n"/>
+      <c r="E108" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F108" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="29" t="n"/>
+      <c r="B109" s="30" t="n"/>
+      <c r="C109" s="31" t="n"/>
+      <c r="D109" s="31" t="n"/>
+      <c r="E109" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F109" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="29" t="n"/>
+      <c r="B110" s="30" t="n"/>
+      <c r="C110" s="31" t="n"/>
+      <c r="D110" s="31" t="n"/>
+      <c r="E110" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F110" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="29" t="n"/>
+      <c r="B111" s="30" t="n"/>
+      <c r="C111" s="31" t="n"/>
+      <c r="D111" s="31" t="n"/>
+      <c r="E111" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F111" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="29" t="n"/>
+      <c r="B112" s="30" t="n"/>
+      <c r="C112" s="31" t="n"/>
+      <c r="D112" s="31" t="n"/>
+      <c r="E112" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F112" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="29" t="n"/>
+      <c r="B113" s="30" t="n"/>
+      <c r="C113" s="31" t="n"/>
+      <c r="D113" s="31" t="n"/>
+      <c r="E113" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F113" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="29" t="n"/>
+      <c r="B114" s="30" t="n"/>
+      <c r="C114" s="31" t="n"/>
+      <c r="D114" s="31" t="n"/>
+      <c r="E114" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F114" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="29" t="n"/>
+      <c r="B115" s="30" t="n"/>
+      <c r="C115" s="31" t="n"/>
+      <c r="D115" s="31" t="n"/>
+      <c r="E115" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F115" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="29" t="n"/>
+      <c r="B116" s="30" t="n"/>
+      <c r="C116" s="31" t="n"/>
+      <c r="D116" s="31" t="n"/>
+      <c r="E116" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F116" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="29" t="n"/>
+      <c r="B117" s="30" t="n"/>
+      <c r="C117" s="31" t="n"/>
+      <c r="D117" s="31" t="n"/>
+      <c r="E117" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F117" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="29" t="n"/>
+      <c r="B118" s="30" t="n"/>
+      <c r="C118" s="31" t="n"/>
+      <c r="D118" s="31" t="n"/>
+      <c r="E118" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F118" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="29" t="n"/>
+      <c r="B119" s="30" t="n"/>
+      <c r="C119" s="31" t="n"/>
+      <c r="D119" s="31" t="n"/>
+      <c r="E119" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F119" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="29" t="n"/>
+      <c r="B120" s="30" t="n"/>
+      <c r="C120" s="31" t="n"/>
+      <c r="D120" s="31" t="n"/>
+      <c r="E120" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F120" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="29" t="n"/>
+      <c r="B121" s="30" t="n"/>
+      <c r="C121" s="31" t="n"/>
+      <c r="D121" s="31" t="n"/>
+      <c r="E121" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F121" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="29" t="n"/>
+      <c r="B122" s="30" t="n"/>
+      <c r="C122" s="31" t="n"/>
+      <c r="D122" s="31" t="n"/>
+      <c r="E122" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F122" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="29" t="n"/>
+      <c r="B123" s="30" t="n"/>
+      <c r="C123" s="31" t="n"/>
+      <c r="D123" s="31" t="n"/>
+      <c r="E123" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F123" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="29" t="n"/>
+      <c r="B124" s="30" t="n"/>
+      <c r="C124" s="31" t="n"/>
+      <c r="D124" s="31" t="n"/>
+      <c r="E124" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F124" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="29" t="n"/>
+      <c r="B125" s="30" t="n"/>
+      <c r="C125" s="31" t="n"/>
+      <c r="D125" s="31" t="n"/>
+      <c r="E125" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F125" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="29" t="n"/>
+      <c r="B126" s="30" t="n"/>
+      <c r="C126" s="31" t="n"/>
+      <c r="D126" s="31" t="n"/>
+      <c r="E126" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F126" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="29" t="n"/>
+      <c r="B127" s="30" t="n"/>
+      <c r="C127" s="31" t="n"/>
+      <c r="D127" s="31" t="n"/>
+      <c r="E127" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F127" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="29" t="n"/>
+      <c r="B128" s="30" t="n"/>
+      <c r="C128" s="31" t="n"/>
+      <c r="D128" s="31" t="n"/>
+      <c r="E128" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F128" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="29" t="n"/>
+      <c r="B129" s="30" t="n"/>
+      <c r="C129" s="31" t="n"/>
+      <c r="D129" s="31" t="n"/>
+      <c r="E129" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F129" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="29" t="n"/>
+      <c r="B130" s="30" t="n"/>
+      <c r="C130" s="31" t="n"/>
+      <c r="D130" s="31" t="n"/>
+      <c r="E130" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F130" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="29" t="n"/>
+      <c r="B131" s="30" t="n"/>
+      <c r="C131" s="31" t="n"/>
+      <c r="D131" s="31" t="n"/>
+      <c r="E131" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F131" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="29" t="n"/>
+      <c r="B132" s="30" t="n"/>
+      <c r="C132" s="31" t="n"/>
+      <c r="D132" s="31" t="n"/>
+      <c r="E132" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F132" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="29" t="n"/>
+      <c r="B133" s="30" t="n"/>
+      <c r="C133" s="31" t="n"/>
+      <c r="D133" s="31" t="n"/>
+      <c r="E133" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F133" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="29" t="n"/>
+      <c r="B134" s="30" t="n"/>
+      <c r="C134" s="31" t="n"/>
+      <c r="D134" s="31" t="n"/>
+      <c r="E134" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F134" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="29" t="n"/>
+      <c r="B135" s="30" t="n"/>
+      <c r="C135" s="31" t="n"/>
+      <c r="D135" s="31" t="n"/>
+      <c r="E135" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F135" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="29" t="n"/>
+      <c r="B136" s="30" t="n"/>
+      <c r="C136" s="31" t="n"/>
+      <c r="D136" s="31" t="n"/>
+      <c r="E136" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F136" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="29" t="n"/>
+      <c r="B137" s="30" t="n"/>
+      <c r="C137" s="31" t="n"/>
+      <c r="D137" s="31" t="n"/>
+      <c r="E137" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F137" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="29" t="n"/>
+      <c r="B138" s="30" t="n"/>
+      <c r="C138" s="31" t="n"/>
+      <c r="D138" s="31" t="n"/>
+      <c r="E138" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F138" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="29" t="n"/>
+      <c r="B139" s="30" t="n"/>
+      <c r="C139" s="31" t="n"/>
+      <c r="D139" s="31" t="n"/>
+      <c r="E139" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F139" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="29" t="n"/>
+      <c r="B140" s="30" t="n"/>
+      <c r="C140" s="31" t="n"/>
+      <c r="D140" s="31" t="n"/>
+      <c r="E140" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F140" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="29" t="n"/>
+      <c r="B141" s="30" t="n"/>
+      <c r="C141" s="31" t="n"/>
+      <c r="D141" s="31" t="n"/>
+      <c r="E141" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F141" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="29" t="n"/>
+      <c r="B142" s="30" t="n"/>
+      <c r="C142" s="31" t="n"/>
+      <c r="D142" s="31" t="n"/>
+      <c r="E142" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F142" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="29" t="n"/>
+      <c r="B143" s="30" t="n"/>
+      <c r="C143" s="31" t="n"/>
+      <c r="D143" s="31" t="n"/>
+      <c r="E143" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F143" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="29" t="n"/>
+      <c r="B144" s="30" t="n"/>
+      <c r="C144" s="31" t="n"/>
+      <c r="D144" s="31" t="n"/>
+      <c r="E144" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F144" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="29" t="n"/>
+      <c r="B145" s="30" t="n"/>
+      <c r="C145" s="31" t="n"/>
+      <c r="D145" s="31" t="n"/>
+      <c r="E145" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F145" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="29" t="n"/>
+      <c r="B146" s="30" t="n"/>
+      <c r="C146" s="31" t="n"/>
+      <c r="D146" s="31" t="n"/>
+      <c r="E146" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F146" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="29" t="n"/>
+      <c r="B147" s="30" t="n"/>
+      <c r="C147" s="31" t="n"/>
+      <c r="D147" s="31" t="n"/>
+      <c r="E147" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F147" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="29" t="n"/>
+      <c r="B148" s="30" t="n"/>
+      <c r="C148" s="31" t="n"/>
+      <c r="D148" s="31" t="n"/>
+      <c r="E148" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F148" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="29" t="n"/>
+      <c r="B149" s="30" t="n"/>
+      <c r="C149" s="31" t="n"/>
+      <c r="D149" s="31" t="n"/>
+      <c r="E149" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F149" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="29" t="n"/>
+      <c r="B150" s="30" t="n"/>
+      <c r="C150" s="31" t="n"/>
+      <c r="D150" s="31" t="n"/>
+      <c r="E150" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F150" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="29" t="n"/>
+      <c r="B151" s="30" t="n"/>
+      <c r="C151" s="31" t="n"/>
+      <c r="D151" s="31" t="n"/>
+      <c r="E151" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F151" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="29" t="n"/>
+      <c r="B152" s="30" t="n"/>
+      <c r="C152" s="31" t="n"/>
+      <c r="D152" s="31" t="n"/>
+      <c r="E152" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F152" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="29" t="n"/>
+      <c r="B153" s="30" t="n"/>
+      <c r="C153" s="31" t="n"/>
+      <c r="D153" s="31" t="n"/>
+      <c r="E153" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F153" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="29" t="n"/>
+      <c r="B154" s="30" t="n"/>
+      <c r="C154" s="31" t="n"/>
+      <c r="D154" s="31" t="n"/>
+      <c r="E154" s="31">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <v/>
+      </c>
+      <c r="F154" s="29">
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Floor_Map_Simple.xlsx
+++ b/Floor_Map_Simple.xlsx
@@ -515,7 +515,7 @@
     <tableColumn id="3" name="Zone"/>
     <tableColumn id="4" name="Low when pallets at or below"/>
     <tableColumn id="5" name="Pallets on map">
-      <calculatedColumnFormula>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" name="Status">
       <calculatedColumnFormula>IF(TRIM(tblStock[[#This Row],[Item code]])="","",IF(tblStock[[#This Row],[Pallets on map]]&lt;=IF(tblStock[[#This Row],[Low when pallets at or below]]="",2,tblStock[[#This Row],[Low when pallets at or below]]),"LOW","OK"))</calculatedColumnFormula>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F5" s="29">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D6" s="31" t="n"/>
       <c r="E6" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F6" s="29">
@@ -2126,7 +2126,7 @@
       <c r="C7" s="31" t="n"/>
       <c r="D7" s="31" t="n"/>
       <c r="E7" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F7" s="29">
@@ -2161,7 +2161,7 @@
       <c r="C8" s="31" t="n"/>
       <c r="D8" s="31" t="n"/>
       <c r="E8" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F8" s="29">
@@ -2196,7 +2196,7 @@
       <c r="C9" s="31" t="n"/>
       <c r="D9" s="31" t="n"/>
       <c r="E9" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F9" s="29">
@@ -2215,7 +2215,7 @@
       <c r="C10" s="31" t="n"/>
       <c r="D10" s="31" t="n"/>
       <c r="E10" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F10" s="29">
@@ -2229,7 +2229,7 @@
       <c r="C11" s="31" t="n"/>
       <c r="D11" s="31" t="n"/>
       <c r="E11" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F11" s="29">
@@ -2243,7 +2243,7 @@
       <c r="C12" s="31" t="n"/>
       <c r="D12" s="31" t="n"/>
       <c r="E12" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F12" s="29">
@@ -2257,7 +2257,7 @@
       <c r="C13" s="31" t="n"/>
       <c r="D13" s="31" t="n"/>
       <c r="E13" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F13" s="29">
@@ -2271,7 +2271,7 @@
       <c r="C14" s="31" t="n"/>
       <c r="D14" s="31" t="n"/>
       <c r="E14" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F14" s="29">
@@ -2285,7 +2285,7 @@
       <c r="C15" s="31" t="n"/>
       <c r="D15" s="31" t="n"/>
       <c r="E15" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F15" s="29">
@@ -2299,7 +2299,7 @@
       <c r="C16" s="31" t="n"/>
       <c r="D16" s="31" t="n"/>
       <c r="E16" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F16" s="29">
@@ -2313,7 +2313,7 @@
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="31" t="n"/>
       <c r="E17" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F17" s="29">
@@ -2327,7 +2327,7 @@
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="31" t="n"/>
       <c r="E18" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F18" s="29">
@@ -2341,7 +2341,7 @@
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="31" t="n"/>
       <c r="E19" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F19" s="29">
@@ -2355,7 +2355,7 @@
       <c r="C20" s="31" t="n"/>
       <c r="D20" s="31" t="n"/>
       <c r="E20" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F20" s="29">
@@ -2369,7 +2369,7 @@
       <c r="C21" s="31" t="n"/>
       <c r="D21" s="31" t="n"/>
       <c r="E21" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F21" s="29">
@@ -2383,7 +2383,7 @@
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="31" t="n"/>
       <c r="E22" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F22" s="29">
@@ -2397,7 +2397,7 @@
       <c r="C23" s="31" t="n"/>
       <c r="D23" s="31" t="n"/>
       <c r="E23" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F23" s="29">
@@ -2411,7 +2411,7 @@
       <c r="C24" s="31" t="n"/>
       <c r="D24" s="31" t="n"/>
       <c r="E24" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F24" s="29">
@@ -2425,7 +2425,7 @@
       <c r="C25" s="31" t="n"/>
       <c r="D25" s="31" t="n"/>
       <c r="E25" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F25" s="29">
@@ -2439,7 +2439,7 @@
       <c r="C26" s="31" t="n"/>
       <c r="D26" s="31" t="n"/>
       <c r="E26" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F26" s="29">
@@ -2453,7 +2453,7 @@
       <c r="C27" s="31" t="n"/>
       <c r="D27" s="31" t="n"/>
       <c r="E27" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F27" s="29">
@@ -2467,7 +2467,7 @@
       <c r="C28" s="31" t="n"/>
       <c r="D28" s="31" t="n"/>
       <c r="E28" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F28" s="29">
@@ -2481,7 +2481,7 @@
       <c r="C29" s="31" t="n"/>
       <c r="D29" s="31" t="n"/>
       <c r="E29" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F29" s="29">
@@ -2495,7 +2495,7 @@
       <c r="C30" s="31" t="n"/>
       <c r="D30" s="31" t="n"/>
       <c r="E30" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F30" s="29">
@@ -2509,7 +2509,7 @@
       <c r="C31" s="31" t="n"/>
       <c r="D31" s="31" t="n"/>
       <c r="E31" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F31" s="29">
@@ -2523,7 +2523,7 @@
       <c r="C32" s="31" t="n"/>
       <c r="D32" s="31" t="n"/>
       <c r="E32" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F32" s="29">
@@ -2537,7 +2537,7 @@
       <c r="C33" s="31" t="n"/>
       <c r="D33" s="31" t="n"/>
       <c r="E33" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F33" s="29">
@@ -2551,7 +2551,7 @@
       <c r="C34" s="31" t="n"/>
       <c r="D34" s="31" t="n"/>
       <c r="E34" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F34" s="29">
@@ -2565,7 +2565,7 @@
       <c r="C35" s="31" t="n"/>
       <c r="D35" s="31" t="n"/>
       <c r="E35" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F35" s="29">
@@ -2579,7 +2579,7 @@
       <c r="C36" s="31" t="n"/>
       <c r="D36" s="31" t="n"/>
       <c r="E36" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F36" s="29">
@@ -2593,7 +2593,7 @@
       <c r="C37" s="31" t="n"/>
       <c r="D37" s="31" t="n"/>
       <c r="E37" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F37" s="29">
@@ -2607,7 +2607,7 @@
       <c r="C38" s="31" t="n"/>
       <c r="D38" s="31" t="n"/>
       <c r="E38" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F38" s="29">
@@ -2621,7 +2621,7 @@
       <c r="C39" s="31" t="n"/>
       <c r="D39" s="31" t="n"/>
       <c r="E39" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F39" s="29">
@@ -2635,7 +2635,7 @@
       <c r="C40" s="31" t="n"/>
       <c r="D40" s="31" t="n"/>
       <c r="E40" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F40" s="29">
@@ -2649,7 +2649,7 @@
       <c r="C41" s="31" t="n"/>
       <c r="D41" s="31" t="n"/>
       <c r="E41" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F41" s="29">
@@ -2663,7 +2663,7 @@
       <c r="C42" s="31" t="n"/>
       <c r="D42" s="31" t="n"/>
       <c r="E42" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F42" s="29">
@@ -2677,7 +2677,7 @@
       <c r="C43" s="31" t="n"/>
       <c r="D43" s="31" t="n"/>
       <c r="E43" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F43" s="29">
@@ -2691,7 +2691,7 @@
       <c r="C44" s="31" t="n"/>
       <c r="D44" s="31" t="n"/>
       <c r="E44" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F44" s="29">
@@ -2705,7 +2705,7 @@
       <c r="C45" s="31" t="n"/>
       <c r="D45" s="31" t="n"/>
       <c r="E45" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F45" s="29">
@@ -2719,7 +2719,7 @@
       <c r="C46" s="31" t="n"/>
       <c r="D46" s="31" t="n"/>
       <c r="E46" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F46" s="29">
@@ -2733,7 +2733,7 @@
       <c r="C47" s="31" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F47" s="29">
@@ -2747,7 +2747,7 @@
       <c r="C48" s="31" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F48" s="29">
@@ -2761,7 +2761,7 @@
       <c r="C49" s="31" t="n"/>
       <c r="D49" s="31" t="n"/>
       <c r="E49" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F49" s="29">
@@ -2775,7 +2775,7 @@
       <c r="C50" s="31" t="n"/>
       <c r="D50" s="31" t="n"/>
       <c r="E50" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F50" s="29">
@@ -2789,7 +2789,7 @@
       <c r="C51" s="31" t="n"/>
       <c r="D51" s="31" t="n"/>
       <c r="E51" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F51" s="29">
@@ -2803,7 +2803,7 @@
       <c r="C52" s="31" t="n"/>
       <c r="D52" s="31" t="n"/>
       <c r="E52" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F52" s="29">
@@ -2817,7 +2817,7 @@
       <c r="C53" s="31" t="n"/>
       <c r="D53" s="31" t="n"/>
       <c r="E53" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F53" s="29">
@@ -2831,7 +2831,7 @@
       <c r="C54" s="31" t="n"/>
       <c r="D54" s="31" t="n"/>
       <c r="E54" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F54" s="29">
@@ -2845,7 +2845,7 @@
       <c r="C55" s="31" t="n"/>
       <c r="D55" s="31" t="n"/>
       <c r="E55" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F55" s="29">
@@ -2859,7 +2859,7 @@
       <c r="C56" s="31" t="n"/>
       <c r="D56" s="31" t="n"/>
       <c r="E56" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F56" s="29">
@@ -2873,7 +2873,7 @@
       <c r="C57" s="31" t="n"/>
       <c r="D57" s="31" t="n"/>
       <c r="E57" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F57" s="29">
@@ -2887,7 +2887,7 @@
       <c r="C58" s="31" t="n"/>
       <c r="D58" s="31" t="n"/>
       <c r="E58" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F58" s="29">
@@ -2901,7 +2901,7 @@
       <c r="C59" s="31" t="n"/>
       <c r="D59" s="31" t="n"/>
       <c r="E59" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F59" s="29">
@@ -2915,7 +2915,7 @@
       <c r="C60" s="31" t="n"/>
       <c r="D60" s="31" t="n"/>
       <c r="E60" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F60" s="29">
@@ -2929,7 +2929,7 @@
       <c r="C61" s="31" t="n"/>
       <c r="D61" s="31" t="n"/>
       <c r="E61" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F61" s="29">
@@ -2943,7 +2943,7 @@
       <c r="C62" s="31" t="n"/>
       <c r="D62" s="31" t="n"/>
       <c r="E62" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F62" s="29">
@@ -2957,7 +2957,7 @@
       <c r="C63" s="31" t="n"/>
       <c r="D63" s="31" t="n"/>
       <c r="E63" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F63" s="29">
@@ -2971,7 +2971,7 @@
       <c r="C64" s="31" t="n"/>
       <c r="D64" s="31" t="n"/>
       <c r="E64" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F64" s="29">
@@ -2985,7 +2985,7 @@
       <c r="C65" s="31" t="n"/>
       <c r="D65" s="31" t="n"/>
       <c r="E65" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F65" s="29">
@@ -2999,7 +2999,7 @@
       <c r="C66" s="31" t="n"/>
       <c r="D66" s="31" t="n"/>
       <c r="E66" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F66" s="29">
@@ -3013,7 +3013,7 @@
       <c r="C67" s="31" t="n"/>
       <c r="D67" s="31" t="n"/>
       <c r="E67" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F67" s="29">
@@ -3027,7 +3027,7 @@
       <c r="C68" s="31" t="n"/>
       <c r="D68" s="31" t="n"/>
       <c r="E68" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F68" s="29">
@@ -3041,7 +3041,7 @@
       <c r="C69" s="31" t="n"/>
       <c r="D69" s="31" t="n"/>
       <c r="E69" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F69" s="29">
@@ -3055,7 +3055,7 @@
       <c r="C70" s="31" t="n"/>
       <c r="D70" s="31" t="n"/>
       <c r="E70" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F70" s="29">
@@ -3069,7 +3069,7 @@
       <c r="C71" s="31" t="n"/>
       <c r="D71" s="31" t="n"/>
       <c r="E71" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F71" s="29">
@@ -3083,7 +3083,7 @@
       <c r="C72" s="31" t="n"/>
       <c r="D72" s="31" t="n"/>
       <c r="E72" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F72" s="29">
@@ -3097,7 +3097,7 @@
       <c r="C73" s="31" t="n"/>
       <c r="D73" s="31" t="n"/>
       <c r="E73" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F73" s="29">
@@ -3111,7 +3111,7 @@
       <c r="C74" s="31" t="n"/>
       <c r="D74" s="31" t="n"/>
       <c r="E74" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F74" s="29">
@@ -3125,7 +3125,7 @@
       <c r="C75" s="31" t="n"/>
       <c r="D75" s="31" t="n"/>
       <c r="E75" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F75" s="29">
@@ -3139,7 +3139,7 @@
       <c r="C76" s="31" t="n"/>
       <c r="D76" s="31" t="n"/>
       <c r="E76" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F76" s="29">
@@ -3153,7 +3153,7 @@
       <c r="C77" s="31" t="n"/>
       <c r="D77" s="31" t="n"/>
       <c r="E77" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F77" s="29">
@@ -3167,7 +3167,7 @@
       <c r="C78" s="31" t="n"/>
       <c r="D78" s="31" t="n"/>
       <c r="E78" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F78" s="29">
@@ -3181,7 +3181,7 @@
       <c r="C79" s="31" t="n"/>
       <c r="D79" s="31" t="n"/>
       <c r="E79" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F79" s="29">
@@ -3195,7 +3195,7 @@
       <c r="C80" s="31" t="n"/>
       <c r="D80" s="31" t="n"/>
       <c r="E80" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F80" s="29">
@@ -3209,7 +3209,7 @@
       <c r="C81" s="31" t="n"/>
       <c r="D81" s="31" t="n"/>
       <c r="E81" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F81" s="29">
@@ -3223,7 +3223,7 @@
       <c r="C82" s="31" t="n"/>
       <c r="D82" s="31" t="n"/>
       <c r="E82" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F82" s="29">
@@ -3237,7 +3237,7 @@
       <c r="C83" s="31" t="n"/>
       <c r="D83" s="31" t="n"/>
       <c r="E83" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F83" s="29">
@@ -3251,7 +3251,7 @@
       <c r="C84" s="31" t="n"/>
       <c r="D84" s="31" t="n"/>
       <c r="E84" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F84" s="29">
@@ -3265,7 +3265,7 @@
       <c r="C85" s="31" t="n"/>
       <c r="D85" s="31" t="n"/>
       <c r="E85" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F85" s="29">
@@ -3279,7 +3279,7 @@
       <c r="C86" s="31" t="n"/>
       <c r="D86" s="31" t="n"/>
       <c r="E86" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F86" s="29">
@@ -3293,7 +3293,7 @@
       <c r="C87" s="31" t="n"/>
       <c r="D87" s="31" t="n"/>
       <c r="E87" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F87" s="29">
@@ -3307,7 +3307,7 @@
       <c r="C88" s="31" t="n"/>
       <c r="D88" s="31" t="n"/>
       <c r="E88" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F88" s="29">
@@ -3321,7 +3321,7 @@
       <c r="C89" s="31" t="n"/>
       <c r="D89" s="31" t="n"/>
       <c r="E89" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F89" s="29">
@@ -3335,7 +3335,7 @@
       <c r="C90" s="31" t="n"/>
       <c r="D90" s="31" t="n"/>
       <c r="E90" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F90" s="29">
@@ -3349,7 +3349,7 @@
       <c r="C91" s="31" t="n"/>
       <c r="D91" s="31" t="n"/>
       <c r="E91" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F91" s="29">
@@ -3363,7 +3363,7 @@
       <c r="C92" s="31" t="n"/>
       <c r="D92" s="31" t="n"/>
       <c r="E92" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F92" s="29">
@@ -3377,7 +3377,7 @@
       <c r="C93" s="31" t="n"/>
       <c r="D93" s="31" t="n"/>
       <c r="E93" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F93" s="29">
@@ -3391,7 +3391,7 @@
       <c r="C94" s="31" t="n"/>
       <c r="D94" s="31" t="n"/>
       <c r="E94" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F94" s="29">
@@ -3405,7 +3405,7 @@
       <c r="C95" s="31" t="n"/>
       <c r="D95" s="31" t="n"/>
       <c r="E95" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F95" s="29">
@@ -3419,7 +3419,7 @@
       <c r="C96" s="31" t="n"/>
       <c r="D96" s="31" t="n"/>
       <c r="E96" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F96" s="29">
@@ -3433,7 +3433,7 @@
       <c r="C97" s="31" t="n"/>
       <c r="D97" s="31" t="n"/>
       <c r="E97" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F97" s="29">
@@ -3447,7 +3447,7 @@
       <c r="C98" s="31" t="n"/>
       <c r="D98" s="31" t="n"/>
       <c r="E98" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F98" s="29">
@@ -3461,7 +3461,7 @@
       <c r="C99" s="31" t="n"/>
       <c r="D99" s="31" t="n"/>
       <c r="E99" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F99" s="29">
@@ -3475,7 +3475,7 @@
       <c r="C100" s="31" t="n"/>
       <c r="D100" s="31" t="n"/>
       <c r="E100" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F100" s="29">
@@ -3489,7 +3489,7 @@
       <c r="C101" s="31" t="n"/>
       <c r="D101" s="31" t="n"/>
       <c r="E101" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F101" s="29">
@@ -3503,7 +3503,7 @@
       <c r="C102" s="31" t="n"/>
       <c r="D102" s="31" t="n"/>
       <c r="E102" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F102" s="29">
@@ -3517,7 +3517,7 @@
       <c r="C103" s="31" t="n"/>
       <c r="D103" s="31" t="n"/>
       <c r="E103" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F103" s="29">
@@ -3531,7 +3531,7 @@
       <c r="C104" s="31" t="n"/>
       <c r="D104" s="31" t="n"/>
       <c r="E104" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F104" s="29">
@@ -3545,7 +3545,7 @@
       <c r="C105" s="31" t="n"/>
       <c r="D105" s="31" t="n"/>
       <c r="E105" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F105" s="29">
@@ -3559,7 +3559,7 @@
       <c r="C106" s="31" t="n"/>
       <c r="D106" s="31" t="n"/>
       <c r="E106" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F106" s="29">
@@ -3573,7 +3573,7 @@
       <c r="C107" s="31" t="n"/>
       <c r="D107" s="31" t="n"/>
       <c r="E107" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F107" s="29">
@@ -3587,7 +3587,7 @@
       <c r="C108" s="31" t="n"/>
       <c r="D108" s="31" t="n"/>
       <c r="E108" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F108" s="29">
@@ -3601,7 +3601,7 @@
       <c r="C109" s="31" t="n"/>
       <c r="D109" s="31" t="n"/>
       <c r="E109" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F109" s="29">
@@ -3615,7 +3615,7 @@
       <c r="C110" s="31" t="n"/>
       <c r="D110" s="31" t="n"/>
       <c r="E110" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F110" s="29">
@@ -3629,7 +3629,7 @@
       <c r="C111" s="31" t="n"/>
       <c r="D111" s="31" t="n"/>
       <c r="E111" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F111" s="29">
@@ -3643,7 +3643,7 @@
       <c r="C112" s="31" t="n"/>
       <c r="D112" s="31" t="n"/>
       <c r="E112" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F112" s="29">
@@ -3657,7 +3657,7 @@
       <c r="C113" s="31" t="n"/>
       <c r="D113" s="31" t="n"/>
       <c r="E113" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F113" s="29">
@@ -3671,7 +3671,7 @@
       <c r="C114" s="31" t="n"/>
       <c r="D114" s="31" t="n"/>
       <c r="E114" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F114" s="29">
@@ -3685,7 +3685,7 @@
       <c r="C115" s="31" t="n"/>
       <c r="D115" s="31" t="n"/>
       <c r="E115" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F115" s="29">
@@ -3699,7 +3699,7 @@
       <c r="C116" s="31" t="n"/>
       <c r="D116" s="31" t="n"/>
       <c r="E116" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F116" s="29">
@@ -3713,7 +3713,7 @@
       <c r="C117" s="31" t="n"/>
       <c r="D117" s="31" t="n"/>
       <c r="E117" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F117" s="29">
@@ -3727,7 +3727,7 @@
       <c r="C118" s="31" t="n"/>
       <c r="D118" s="31" t="n"/>
       <c r="E118" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F118" s="29">
@@ -3741,7 +3741,7 @@
       <c r="C119" s="31" t="n"/>
       <c r="D119" s="31" t="n"/>
       <c r="E119" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F119" s="29">
@@ -3755,7 +3755,7 @@
       <c r="C120" s="31" t="n"/>
       <c r="D120" s="31" t="n"/>
       <c r="E120" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F120" s="29">
@@ -3769,7 +3769,7 @@
       <c r="C121" s="31" t="n"/>
       <c r="D121" s="31" t="n"/>
       <c r="E121" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F121" s="29">
@@ -3783,7 +3783,7 @@
       <c r="C122" s="31" t="n"/>
       <c r="D122" s="31" t="n"/>
       <c r="E122" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F122" s="29">
@@ -3797,7 +3797,7 @@
       <c r="C123" s="31" t="n"/>
       <c r="D123" s="31" t="n"/>
       <c r="E123" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F123" s="29">
@@ -3811,7 +3811,7 @@
       <c r="C124" s="31" t="n"/>
       <c r="D124" s="31" t="n"/>
       <c r="E124" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F124" s="29">
@@ -3825,7 +3825,7 @@
       <c r="C125" s="31" t="n"/>
       <c r="D125" s="31" t="n"/>
       <c r="E125" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F125" s="29">
@@ -3839,7 +3839,7 @@
       <c r="C126" s="31" t="n"/>
       <c r="D126" s="31" t="n"/>
       <c r="E126" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F126" s="29">
@@ -3853,7 +3853,7 @@
       <c r="C127" s="31" t="n"/>
       <c r="D127" s="31" t="n"/>
       <c r="E127" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F127" s="29">
@@ -3867,7 +3867,7 @@
       <c r="C128" s="31" t="n"/>
       <c r="D128" s="31" t="n"/>
       <c r="E128" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F128" s="29">
@@ -3881,7 +3881,7 @@
       <c r="C129" s="31" t="n"/>
       <c r="D129" s="31" t="n"/>
       <c r="E129" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F129" s="29">
@@ -3895,7 +3895,7 @@
       <c r="C130" s="31" t="n"/>
       <c r="D130" s="31" t="n"/>
       <c r="E130" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F130" s="29">
@@ -3909,7 +3909,7 @@
       <c r="C131" s="31" t="n"/>
       <c r="D131" s="31" t="n"/>
       <c r="E131" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F131" s="29">
@@ -3923,7 +3923,7 @@
       <c r="C132" s="31" t="n"/>
       <c r="D132" s="31" t="n"/>
       <c r="E132" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F132" s="29">
@@ -3937,7 +3937,7 @@
       <c r="C133" s="31" t="n"/>
       <c r="D133" s="31" t="n"/>
       <c r="E133" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F133" s="29">
@@ -3951,7 +3951,7 @@
       <c r="C134" s="31" t="n"/>
       <c r="D134" s="31" t="n"/>
       <c r="E134" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F134" s="29">
@@ -3965,7 +3965,7 @@
       <c r="C135" s="31" t="n"/>
       <c r="D135" s="31" t="n"/>
       <c r="E135" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F135" s="29">
@@ -3979,7 +3979,7 @@
       <c r="C136" s="31" t="n"/>
       <c r="D136" s="31" t="n"/>
       <c r="E136" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F136" s="29">
@@ -3993,7 +3993,7 @@
       <c r="C137" s="31" t="n"/>
       <c r="D137" s="31" t="n"/>
       <c r="E137" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F137" s="29">
@@ -4007,7 +4007,7 @@
       <c r="C138" s="31" t="n"/>
       <c r="D138" s="31" t="n"/>
       <c r="E138" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F138" s="29">
@@ -4021,7 +4021,7 @@
       <c r="C139" s="31" t="n"/>
       <c r="D139" s="31" t="n"/>
       <c r="E139" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F139" s="29">
@@ -4035,7 +4035,7 @@
       <c r="C140" s="31" t="n"/>
       <c r="D140" s="31" t="n"/>
       <c r="E140" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F140" s="29">
@@ -4049,7 +4049,7 @@
       <c r="C141" s="31" t="n"/>
       <c r="D141" s="31" t="n"/>
       <c r="E141" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F141" s="29">
@@ -4063,7 +4063,7 @@
       <c r="C142" s="31" t="n"/>
       <c r="D142" s="31" t="n"/>
       <c r="E142" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F142" s="29">
@@ -4077,7 +4077,7 @@
       <c r="C143" s="31" t="n"/>
       <c r="D143" s="31" t="n"/>
       <c r="E143" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F143" s="29">
@@ -4091,7 +4091,7 @@
       <c r="C144" s="31" t="n"/>
       <c r="D144" s="31" t="n"/>
       <c r="E144" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F144" s="29">
@@ -4105,7 +4105,7 @@
       <c r="C145" s="31" t="n"/>
       <c r="D145" s="31" t="n"/>
       <c r="E145" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F145" s="29">
@@ -4119,7 +4119,7 @@
       <c r="C146" s="31" t="n"/>
       <c r="D146" s="31" t="n"/>
       <c r="E146" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F146" s="29">
@@ -4133,7 +4133,7 @@
       <c r="C147" s="31" t="n"/>
       <c r="D147" s="31" t="n"/>
       <c r="E147" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F147" s="29">
@@ -4147,7 +4147,7 @@
       <c r="C148" s="31" t="n"/>
       <c r="D148" s="31" t="n"/>
       <c r="E148" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F148" s="29">
@@ -4161,7 +4161,7 @@
       <c r="C149" s="31" t="n"/>
       <c r="D149" s="31" t="n"/>
       <c r="E149" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F149" s="29">
@@ -4175,7 +4175,7 @@
       <c r="C150" s="31" t="n"/>
       <c r="D150" s="31" t="n"/>
       <c r="E150" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F150" s="29">
@@ -4189,7 +4189,7 @@
       <c r="C151" s="31" t="n"/>
       <c r="D151" s="31" t="n"/>
       <c r="E151" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F151" s="29">
@@ -4203,7 +4203,7 @@
       <c r="C152" s="31" t="n"/>
       <c r="D152" s="31" t="n"/>
       <c r="E152" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F152" s="29">
@@ -4217,7 +4217,7 @@
       <c r="C153" s="31" t="n"/>
       <c r="D153" s="31" t="n"/>
       <c r="E153" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F153" s="29">
@@ -4231,7 +4231,7 @@
       <c r="C154" s="31" t="n"/>
       <c r="D154" s="31" t="n"/>
       <c r="E154" s="31">
-        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$DZ$300,TRIM(tblStock[[#This Row],[Item code]])))</f>
+        <f>IF(TRIM(tblStock[[#This Row],[Item code]])="","",COUNTIF(Map!$A$6:$ZZ$2000,TRIM(tblStock[[#This Row],[Item code]])))</f>
         <v/>
       </c>
       <c r="F154" s="29">
